--- a/outputs/planning/策划参数.xlsx
+++ b/outputs/planning/策划参数.xlsx
@@ -2,14 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用与量级" sheetId="1" r:id="R0383ad5ea5644a71"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01 判定与容错" sheetId="2" r:id="Ref98fad1847746b6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02 魂火与惩罚" sheetId="3" r:id="Rd859c9b19e0a4e32"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03 调频" sheetId="4" r:id="R5b622f124cc34db6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04 计分" sheetId="5" r:id="Rfd031c719bbc4c86"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05 读谱与声波" sheetId="6" r:id="Rc6fc881398bf4c5f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06 随从" sheetId="7" r:id="Rcb191fc7d31c4757"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07 分界线表现" sheetId="8" r:id="R3f2052684711490e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用与量级" sheetId="1" r:id="R7e9e5ef89e184007"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01 判定与容错" sheetId="2" r:id="R2fc62e90be4647fc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02 魂火与惩罚" sheetId="3" r:id="R1d2d5e8a20074594"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03 调频" sheetId="4" r:id="R5681c944c0e94330"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04 计分" sheetId="5" r:id="Rcefc1ec2af874d3f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05 读谱与声波" sheetId="6" r:id="Rc2dbb7191e744b80"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06 随从" sheetId="7" r:id="R5f4dfb744e6f4c19"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07 分界线表现" sheetId="8" r:id="Rae3e894d829c49a5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08 角色移动" sheetId="9" r:id="Rfb89b7fbc8bd4723"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -20,13 +21,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="7">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="0.0%"/>
     <x:numFmt numFmtId="202" formatCode="0.00"/>
     <x:numFmt numFmtId="203" formatCode="0%"/>
     <x:numFmt numFmtId="204" formatCode="0.000"/>
     <x:numFmt numFmtId="205" formatCode="0.0000"/>
+    <x:numFmt numFmtId="206" formatCode="@"/>
   </x:numFmts>
   <x:fonts count="4">
     <x:font>
@@ -51,7 +53,7 @@
       <x:name val="Microsoft YaHei"/>
     </x:font>
   </x:fonts>
-  <x:fills count="7">
+  <x:fills count="16">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -83,6 +85,51 @@
         <x:fgColor rgb="FFFFF0C2"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF0C2"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE7E8EA"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE7E8EA"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF0C2"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE7E8EA"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF3F5967"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF0C2"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE7E8EA"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE7E8EA"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="1">
     <x:border/>
@@ -90,7 +137,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="28">
+  <x:cellXfs count="53">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -155,6 +202,77 @@
       <x:alignment vertical="center"/>
     </x:xf>
     <x:xf numFmtId="205" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="205" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="205" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="205" fontId="1" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="205" fontId="1" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="1" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="205" fontId="1" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="205" fontId="1" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="206" fontId="1" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="206" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="205" fontId="1" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="206" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="205" fontId="1" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
   </x:cellXfs>
@@ -2908,9 +3026,9 @@
     </x:row>
     <x:row r="7" ht="46" customHeight="1">
       <x:c r="A7" s="6" t="str">
-        <x:v>缓流周期</x:v>
-      </x:c>
-      <x:c r="B7" s="21" t="n">
+        <x:v>已停用：缓流周期</x:v>
+      </x:c>
+      <x:c r="B7" s="51" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="C7" s="20" t="n">
@@ -2928,21 +3046,17 @@
       <x:c r="G7" s="8" t="str">
         <x:v>一轮抬浪、回卷、舒展的总时长；换景保持歌曲相位。</x:v>
       </x:c>
-      <x:c r="H7" s="6" t="str">
-        <x:v>boundary</x:v>
-      </x:c>
-      <x:c r="I7" s="6" t="str">
-        <x:v>period_sec</x:v>
-      </x:c>
+      <x:c r="H7" s="6" t="str"/>
+      <x:c r="I7" s="6" t="str"/>
       <x:c r="J7" s="6" t="str">
         <x:v>src/content/resources/boundary_motion_style.gd</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="46" customHeight="1">
       <x:c r="A8" s="6" t="str">
-        <x:v>水带起伏</x:v>
-      </x:c>
-      <x:c r="B8" s="21" t="n">
+        <x:v>已停用：水带起伏</x:v>
+      </x:c>
+      <x:c r="B8" s="51" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C8" s="20" t="n">
@@ -2960,21 +3074,17 @@
       <x:c r="G8" s="8" t="str">
         <x:v>1920×1080 基准下的水带幅度；连接带和中央内缘保持稳定。</x:v>
       </x:c>
-      <x:c r="H8" s="6" t="str">
-        <x:v>boundary</x:v>
-      </x:c>
-      <x:c r="I8" s="6" t="str">
-        <x:v>stream_amplitude_px</x:v>
-      </x:c>
+      <x:c r="H8" s="6" t="str"/>
+      <x:c r="I8" s="6" t="str"/>
       <x:c r="J8" s="6" t="str">
         <x:v>src/content/resources/boundary_motion_style.gd</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="46" customHeight="1">
       <x:c r="A9" s="6" t="str">
-        <x:v>大浪回卷</x:v>
-      </x:c>
-      <x:c r="B9" s="21" t="n">
+        <x:v>已停用：大浪回卷</x:v>
+      </x:c>
+      <x:c r="B9" s="51" t="n">
         <x:v>12</x:v>
       </x:c>
       <x:c r="C9" s="20" t="n">
@@ -2992,21 +3102,17 @@
       <x:c r="G9" s="8" t="str">
         <x:v>大浪身与浪尖的局部行程，按控制图平滑衰减。</x:v>
       </x:c>
-      <x:c r="H9" s="6" t="str">
-        <x:v>boundary</x:v>
-      </x:c>
-      <x:c r="I9" s="6" t="str">
-        <x:v>curl_amplitude_px</x:v>
-      </x:c>
+      <x:c r="H9" s="6" t="str"/>
+      <x:c r="I9" s="6" t="str"/>
       <x:c r="J9" s="6" t="str">
         <x:v>src/content/resources/boundary_motion_style.gd</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="46" customHeight="1">
       <x:c r="A10" s="6" t="str">
-        <x:v>节拍回应</x:v>
-      </x:c>
-      <x:c r="B10" s="9" t="n">
+        <x:v>已停用：节拍回应</x:v>
+      </x:c>
+      <x:c r="B10" s="52" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C10" s="10" t="n">
@@ -3024,21 +3130,17 @@
       <x:c r="G10" s="8" t="str">
         <x:v>按谱面每拍叠加轻微舒张；关闭后仍可保留缓流。</x:v>
       </x:c>
-      <x:c r="H10" s="6" t="str">
-        <x:v>boundary</x:v>
-      </x:c>
-      <x:c r="I10" s="6" t="str">
-        <x:v>beat_enabled</x:v>
-      </x:c>
+      <x:c r="H10" s="6" t="str"/>
+      <x:c r="I10" s="6" t="str"/>
       <x:c r="J10" s="6" t="str">
         <x:v>src/content/resources/boundary_motion_style.gd</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="46" customHeight="1">
       <x:c r="A11" s="6" t="str">
-        <x:v>节拍舒张幅度</x:v>
-      </x:c>
-      <x:c r="B11" s="21" t="n">
+        <x:v>已停用：节拍舒张幅度</x:v>
+      </x:c>
+      <x:c r="B11" s="51" t="n">
         <x:v>1.2</x:v>
       </x:c>
       <x:c r="C11" s="20" t="n">
@@ -3056,18 +3158,302 @@
       <x:c r="G11" s="8" t="str">
         <x:v>拍点后 0.18 拍达峰、0.80 拍前回落；浪尖为此值的至多 1.5 倍，不累积。</x:v>
       </x:c>
-      <x:c r="H11" s="6" t="str">
-        <x:v>boundary</x:v>
-      </x:c>
-      <x:c r="I11" s="6" t="str">
-        <x:v>beat_amplitude_px</x:v>
-      </x:c>
+      <x:c r="H11" s="6" t="str"/>
+      <x:c r="I11" s="6" t="str"/>
       <x:c r="J11" s="6" t="str">
         <x:v>src/content/resources/boundary_motion_style.gd</x:v>
       </x:c>
     </x:row>
+    <x:row r="12" ht="46" customHeight="1">
+      <x:c r="A12" s="6" t="str">
+        <x:v>大浪间隔</x:v>
+      </x:c>
+      <x:c r="B12" s="9" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C12" s="10" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D12" s="6" t="str">
+        <x:v>小节</x:v>
+      </x:c>
+      <x:c r="E12" s="6" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F12" s="10" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G12" s="8" t="str">
+        <x:v>每隔此数小节首拍拍落一对大浪；每道浪持续两小节。</x:v>
+      </x:c>
+      <x:c r="H12" s="6" t="str">
+        <x:v>boundary</x:v>
+      </x:c>
+      <x:c r="I12" s="6" t="str">
+        <x:v>bar_interval</x:v>
+      </x:c>
+      <x:c r="J12" s="6" t="str">
+        <x:v>src/content/resources/boundary_motion_style.gd</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="46" customHeight="1">
+      <x:c r="A13" s="6" t="str">
+        <x:v>大浪高度</x:v>
+      </x:c>
+      <x:c r="B13" s="21" t="n">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="C13" s="20" t="n">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="D13" s="6" t="str">
+        <x:v>设计 px</x:v>
+      </x:c>
+      <x:c r="E13" s="6" t="str">
+        <x:v>150～170</x:v>
+      </x:c>
+      <x:c r="F13" s="10" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G13" s="8" t="str">
+        <x:v>最高伸顶姿势的高度；修改后检查判定圈周围留白。</x:v>
+      </x:c>
+      <x:c r="H13" s="6" t="str">
+        <x:v>boundary</x:v>
+      </x:c>
+      <x:c r="I13" s="6" t="str">
+        <x:v>wave_height_px</x:v>
+      </x:c>
+      <x:c r="J13" s="6" t="str">
+        <x:v>src/content/resources/boundary_motion_style.gd</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="46" customHeight="1">
+      <x:c r="A14" s="6" t="str">
+        <x:v>浪身推进</x:v>
+      </x:c>
+      <x:c r="B14" s="21" t="n">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="C14" s="20" t="n">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="D14" s="6" t="str">
+        <x:v>设计 px</x:v>
+      </x:c>
+      <x:c r="E14" s="6" t="str">
+        <x:v>160～200</x:v>
+      </x:c>
+      <x:c r="F14" s="10" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G14" s="8" t="str">
+        <x:v>从低水脊到触水的前进距离；水沫随后再前滑约 120 px。</x:v>
+      </x:c>
+      <x:c r="H14" s="6" t="str">
+        <x:v>boundary</x:v>
+      </x:c>
+      <x:c r="I14" s="6" t="str">
+        <x:v>advance_px</x:v>
+      </x:c>
+      <x:c r="J14" s="6" t="str">
+        <x:v>src/content/resources/boundary_motion_style.gd</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="46" customHeight="1">
+      <x:c r="A15" s="6" t="str">
+        <x:v>翻卷行程</x:v>
+      </x:c>
+      <x:c r="B15" s="21" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C15" s="20" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="D15" s="6" t="str">
+        <x:v>设计 px</x:v>
+      </x:c>
+      <x:c r="E15" s="6" t="str">
+        <x:v>70～110</x:v>
+      </x:c>
+      <x:c r="F15" s="10" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G15" s="8" t="str">
+        <x:v>控制浪唇横向舒展与翻送尺度，浪高独立配置。</x:v>
+      </x:c>
+      <x:c r="H15" s="6" t="str">
+        <x:v>boundary</x:v>
+      </x:c>
+      <x:c r="I15" s="6" t="str">
+        <x:v>curl_travel_px</x:v>
+      </x:c>
+      <x:c r="J15" s="6" t="str">
+        <x:v>src/content/resources/boundary_motion_style.gd</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="46" customHeight="1">
+      <x:c r="A16" s="6" t="str">
+        <x:v>白沫强度</x:v>
+      </x:c>
+      <x:c r="B16" s="11" t="n">
+        <x:v>0.9</x:v>
+      </x:c>
+      <x:c r="C16" s="12" t="n">
+        <x:v>0.9</x:v>
+      </x:c>
+      <x:c r="D16" s="6" t="str">
+        <x:v>比例</x:v>
+      </x:c>
+      <x:c r="E16" s="6" t="str">
+        <x:v>60%～100%</x:v>
+      </x:c>
+      <x:c r="F16" s="12" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="G16" s="8" t="str">
+        <x:v>只控制拍落后白沫和细水线的不透明度。</x:v>
+      </x:c>
+      <x:c r="H16" s="6" t="str">
+        <x:v>boundary</x:v>
+      </x:c>
+      <x:c r="I16" s="6" t="str">
+        <x:v>foam_strength</x:v>
+      </x:c>
+      <x:c r="J16" s="6" t="str">
+        <x:v>src/content/resources/boundary_motion_style.gd</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="46" customHeight="1">
+      <x:c r="A17" s="6" t="str">
+        <x:v>基底水流</x:v>
+      </x:c>
+      <x:c r="B17" s="9" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C17" s="10" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D17" s="6" t="str">
+        <x:v>开关</x:v>
+      </x:c>
+      <x:c r="E17" s="6" t="str">
+        <x:v>开启</x:v>
+      </x:c>
+      <x:c r="F17" s="10" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G17" s="8" t="str">
+        <x:v>关闭后基底原纹固定，活动浪头继续播放；总动画关闭时仍恢复完整原画。</x:v>
+      </x:c>
+      <x:c r="H17" s="6" t="str">
+        <x:v>boundary</x:v>
+      </x:c>
+      <x:c r="I17" s="6" t="str">
+        <x:v>flow_enabled</x:v>
+      </x:c>
+      <x:c r="J17" s="6" t="str">
+        <x:v>src/content/resources/boundary_motion_style.gd</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="46" customHeight="1">
+      <x:c r="A18" s="6" t="str">
+        <x:v>基底流速</x:v>
+      </x:c>
+      <x:c r="B18" s="21" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="C18" s="20" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="D18" s="6" t="str">
+        <x:v>设计 px/s</x:v>
+      </x:c>
+      <x:c r="E18" s="6" t="str">
+        <x:v>48～72</x:v>
+      </x:c>
+      <x:c r="F18" s="10" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G18" s="8" t="str">
+        <x:v>内部色带的基准流速；局部随水带宽窄变化，不随 BPM 加速。</x:v>
+      </x:c>
+      <x:c r="H18" s="6" t="str">
+        <x:v>boundary</x:v>
+      </x:c>
+      <x:c r="I18" s="6" t="str">
+        <x:v>flow_speed_px_sec</x:v>
+      </x:c>
+      <x:c r="J18" s="6" t="str">
+        <x:v>src/content/resources/boundary_motion_style.gd</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="46" customHeight="1">
+      <x:c r="A19" s="6" t="str">
+        <x:v>原纹流动强度</x:v>
+      </x:c>
+      <x:c r="B19" s="11" t="n">
+        <x:v>0.8</x:v>
+      </x:c>
+      <x:c r="C19" s="12" t="n">
+        <x:v>0.8</x:v>
+      </x:c>
+      <x:c r="D19" s="6" t="str">
+        <x:v>比例</x:v>
+      </x:c>
+      <x:c r="E19" s="6" t="str">
+        <x:v>65%～90%</x:v>
+      </x:c>
+      <x:c r="F19" s="12" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="G19" s="8" t="str">
+        <x:v>内部流动颜色的混合比例；不改变透明轮廓和水带厚度。</x:v>
+      </x:c>
+      <x:c r="H19" s="6" t="str">
+        <x:v>boundary</x:v>
+      </x:c>
+      <x:c r="I19" s="6" t="str">
+        <x:v>flow_strength</x:v>
+      </x:c>
+      <x:c r="J19" s="6" t="str">
+        <x:v>src/content/resources/boundary_motion_style.gd</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="46" customHeight="1">
+      <x:c r="A20" s="6" t="str">
+        <x:v>细水纹强度</x:v>
+      </x:c>
+      <x:c r="B20" s="11" t="n">
+        <x:v>0.24</x:v>
+      </x:c>
+      <x:c r="C20" s="12" t="n">
+        <x:v>0.24</x:v>
+      </x:c>
+      <x:c r="D20" s="6" t="str">
+        <x:v>比例</x:v>
+      </x:c>
+      <x:c r="E20" s="6" t="str">
+        <x:v>18%～30%</x:v>
+      </x:c>
+      <x:c r="F20" s="12" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="G20" s="8" t="str">
+        <x:v>原画色细水线的峰值混合比例；0 只关闭细纹，不影响原纹流动。</x:v>
+      </x:c>
+      <x:c r="H20" s="6" t="str">
+        <x:v>boundary</x:v>
+      </x:c>
+      <x:c r="I20" s="6" t="str">
+        <x:v>streak_strength</x:v>
+      </x:c>
+      <x:c r="J20" s="6" t="str">
+        <x:v>src/content/resources/boundary_motion_style.gd</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:dataValidations count="6">
+  <x:dataValidations count="15">
     <x:dataValidation type="whole" operator="between" sqref="B6">
       <x:formula1>0</x:formula1>
       <x:formula2>1</x:formula2>
@@ -3091,6 +3477,309 @@
     <x:dataValidation type="decimal" operator="between" sqref="B11">
       <x:formula1>0</x:formula1>
       <x:formula2>2</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="whole" operator="between" sqref="B12">
+      <x:formula1>1</x:formula1>
+      <x:formula2>4</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="decimal" operator="between" sqref="B13">
+      <x:formula1>100</x:formula1>
+      <x:formula2>190</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="decimal" operator="between" sqref="B14">
+      <x:formula1>100</x:formula1>
+      <x:formula2>240</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="decimal" operator="between" sqref="B15">
+      <x:formula1>70</x:formula1>
+      <x:formula2>110</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="decimal" operator="between" sqref="B16">
+      <x:formula1>0</x:formula1>
+      <x:formula2>1</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="whole" operator="between" sqref="B17">
+      <x:formula1>0</x:formula1>
+      <x:formula2>1</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="decimal" operator="between" sqref="B18">
+      <x:formula1>0</x:formula1>
+      <x:formula2>100</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="decimal" operator="between" sqref="B19">
+      <x:formula1>0</x:formula1>
+      <x:formula2>1</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="decimal" operator="between" sqref="B20">
+      <x:formula1>0</x:formula1>
+      <x:formula2>0.4</x:formula2>
+    </x:dataValidation>
+  </x:dataValidations>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="15" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="30" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="72" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="32" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="40" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="58" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="2">
+      <x:c r="A2" s="2" t="str">
+        <x:v>角色移动</x:v>
+      </x:c>
+      <x:c r="B2" s="1"/>
+      <x:c r="C2" s="1"/>
+      <x:c r="D2" s="1"/>
+      <x:c r="E2" s="1"/>
+      <x:c r="F2" s="1"/>
+      <x:c r="G2" s="1"/>
+      <x:c r="H2" s="1"/>
+      <x:c r="I2" s="1"/>
+      <x:c r="J2" s="1"/>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="1" t="str">
+        <x:v>修改黄色当前值；参考层填写连续性标识，留空使用静息。</x:v>
+      </x:c>
+      <x:c r="B3" s="1"/>
+      <x:c r="C3" s="1"/>
+      <x:c r="D3" s="1"/>
+      <x:c r="E3" s="1"/>
+      <x:c r="F3" s="1"/>
+      <x:c r="G3" s="1"/>
+      <x:c r="H3" s="1"/>
+      <x:c r="I3" s="1"/>
+      <x:c r="J3" s="1"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="1"/>
+      <x:c r="B4" s="1"/>
+      <x:c r="C4" s="1"/>
+      <x:c r="D4" s="1"/>
+      <x:c r="E4" s="1"/>
+      <x:c r="F4" s="1"/>
+      <x:c r="G4" s="1"/>
+      <x:c r="H4" s="1"/>
+      <x:c r="I4" s="1"/>
+      <x:c r="J4" s="1"/>
+    </x:row>
+    <x:row r="5" ht="30" customHeight="1">
+      <x:c r="A5" s="43" t="str">
+        <x:v>参数</x:v>
+      </x:c>
+      <x:c r="B5" s="43" t="str">
+        <x:v>当前值</x:v>
+      </x:c>
+      <x:c r="C5" s="43" t="str">
+        <x:v>原型默认</x:v>
+      </x:c>
+      <x:c r="D5" s="43" t="str">
+        <x:v>单位</x:v>
+      </x:c>
+      <x:c r="E5" s="43" t="str">
+        <x:v>建议试调区间</x:v>
+      </x:c>
+      <x:c r="F5" s="43" t="str">
+        <x:v>每次建议改动</x:v>
+      </x:c>
+      <x:c r="G5" s="43" t="str">
+        <x:v>作用与注意事项</x:v>
+      </x:c>
+      <x:c r="H5" s="43" t="str">
+        <x:v>配置对象</x:v>
+      </x:c>
+      <x:c r="I5" s="43" t="str">
+        <x:v>字段名</x:v>
+      </x:c>
+      <x:c r="J5" s="43" t="str">
+        <x:v>来源（Game 内）</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="46" customHeight="1">
+      <x:c r="A6" s="6" t="str">
+        <x:v>移动循环时长</x:v>
+      </x:c>
+      <x:c r="B6" s="21" t="n">
+        <x:v>1.6</x:v>
+      </x:c>
+      <x:c r="C6" s="20" t="n">
+        <x:v>1.6</x:v>
+      </x:c>
+      <x:c r="D6" s="6" t="str">
+        <x:v>秒</x:v>
+      </x:c>
+      <x:c r="E6" s="6" t="str">
+        <x:v>0.8～3.2</x:v>
+      </x:c>
+      <x:c r="F6" s="20" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="G6" s="8" t="str">
+        <x:v>一轮包含左右两步；固定步频，不随 BPM 或发波变化。</x:v>
+      </x:c>
+      <x:c r="H6" s="6" t="str">
+        <x:v>actors</x:v>
+      </x:c>
+      <x:c r="I6" s="6" t="str">
+        <x:v>walk_period_sec</x:v>
+      </x:c>
+      <x:c r="J6" s="6" t="str">
+        <x:v>src/content/resources/stage_visual_theme.gd</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="46" customHeight="1">
+      <x:c r="A7" s="6" t="str">
+        <x:v>移动启停混合</x:v>
+      </x:c>
+      <x:c r="B7" s="21" t="n">
+        <x:v>0.18</x:v>
+      </x:c>
+      <x:c r="C7" s="20" t="n">
+        <x:v>0.18</x:v>
+      </x:c>
+      <x:c r="D7" s="6" t="str">
+        <x:v>秒</x:v>
+      </x:c>
+      <x:c r="E7" s="6" t="str">
+        <x:v>0.05～0.4</x:v>
+      </x:c>
+      <x:c r="F7" s="20" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="G7" s="8" t="str">
+        <x:v>地景启动、停止时与静息的衔接时间；攻击收招仍使用 0.15 秒。</x:v>
+      </x:c>
+      <x:c r="H7" s="6" t="str">
+        <x:v>actors</x:v>
+      </x:c>
+      <x:c r="I7" s="6" t="str">
+        <x:v>walk_mix_sec</x:v>
+      </x:c>
+      <x:c r="J7" s="6" t="str">
+        <x:v>src/content/resources/stage_visual_theme.gd</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="46" customHeight="1">
+      <x:c r="A8" s="6" t="str">
+        <x:v>地景停止阈值</x:v>
+      </x:c>
+      <x:c r="B8" s="21" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="C8" s="20" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="D8" s="6" t="str">
+        <x:v>设计 px/s</x:v>
+      </x:c>
+      <x:c r="E8" s="6" t="str">
+        <x:v>0.01～10</x:v>
+      </x:c>
+      <x:c r="F8" s="20" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="G8" s="8" t="str">
+        <x:v>主场景沿滚动方向的实际速度低于此值时静息，排除震屏和手持晃动。</x:v>
+      </x:c>
+      <x:c r="H8" s="6" t="str">
+        <x:v>actors</x:v>
+      </x:c>
+      <x:c r="I8" s="6" t="str">
+        <x:v>walk_stop_speed_px_sec</x:v>
+      </x:c>
+      <x:c r="J8" s="6" t="str">
+        <x:v>src/content/resources/stage_visual_theme.gd</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="46" customHeight="1">
+      <x:c r="A9" s="6" t="str">
+        <x:v>生侧移动参考层</x:v>
+      </x:c>
+      <x:c r="B9" s="50" t="str">
+        <x:v>50/default</x:v>
+      </x:c>
+      <x:c r="C9" s="47" t="str">
+        <x:v>50/default</x:v>
+      </x:c>
+      <x:c r="D9" s="6" t="str">
+        <x:v>连续性标识</x:v>
+      </x:c>
+      <x:c r="E9" s="6" t="str">
+        <x:v>按主地景配置</x:v>
+      </x:c>
+      <x:c r="F9" s="10" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G9" s="8" t="str">
+        <x:v>主地景连续性标识；当前五份背景的远景生侧，缺失或留空时静息。</x:v>
+      </x:c>
+      <x:c r="H9" s="6" t="str">
+        <x:v>actors</x:v>
+      </x:c>
+      <x:c r="I9" s="6" t="str">
+        <x:v>life_movement_layer_key</x:v>
+      </x:c>
+      <x:c r="J9" s="6" t="str">
+        <x:v>src/content/resources/stage_visual_theme.gd</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="46" customHeight="1">
+      <x:c r="A10" s="6" t="str">
+        <x:v>死侧移动参考层</x:v>
+      </x:c>
+      <x:c r="B10" s="50" t="str">
+        <x:v>50/sublayer_55</x:v>
+      </x:c>
+      <x:c r="C10" s="47" t="str">
+        <x:v>50/sublayer_55</x:v>
+      </x:c>
+      <x:c r="D10" s="6" t="str">
+        <x:v>连续性标识</x:v>
+      </x:c>
+      <x:c r="E10" s="6" t="str">
+        <x:v>按主地景配置</x:v>
+      </x:c>
+      <x:c r="F10" s="10" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G10" s="8" t="str">
+        <x:v>主地景连续性标识；当前五份背景的远景死侧，缺失或留空时静息。</x:v>
+      </x:c>
+      <x:c r="H10" s="6" t="str">
+        <x:v>actors</x:v>
+      </x:c>
+      <x:c r="I10" s="6" t="str">
+        <x:v>death_movement_layer_key</x:v>
+      </x:c>
+      <x:c r="J10" s="6" t="str">
+        <x:v>src/content/resources/stage_visual_theme.gd</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:dataValidations count="3">
+    <x:dataValidation type="decimal" operator="between" sqref="B6">
+      <x:formula1>0.8</x:formula1>
+      <x:formula2>3.2</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="decimal" operator="between" sqref="B7">
+      <x:formula1>0.05</x:formula1>
+      <x:formula2>0.4</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="decimal" operator="between" sqref="B8">
+      <x:formula1>0.01</x:formula1>
+      <x:formula2>10</x:formula2>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/outputs/planning/策划参数.xlsx
+++ b/outputs/planning/策划参数.xlsx
@@ -2,15 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用与量级" sheetId="1" r:id="R7e9e5ef89e184007"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01 判定与容错" sheetId="2" r:id="R2fc62e90be4647fc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02 魂火与惩罚" sheetId="3" r:id="R1d2d5e8a20074594"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03 调频" sheetId="4" r:id="R5681c944c0e94330"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04 计分" sheetId="5" r:id="Rcefc1ec2af874d3f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05 读谱与声波" sheetId="6" r:id="Rc2dbb7191e744b80"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06 随从" sheetId="7" r:id="R5f4dfb744e6f4c19"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07 分界线表现" sheetId="8" r:id="Rae3e894d829c49a5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08 角色移动" sheetId="9" r:id="Rfb89b7fbc8bd4723"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用与量级" sheetId="1" r:id="Raad4d06ba1034db4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01 判定与容错" sheetId="2" r:id="R517b9f7929154c5e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02 魂火与惩罚" sheetId="3" r:id="Rfda77c3f4e3b42c9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03 调频" sheetId="4" r:id="R27630d1f84a5484f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04 计分" sheetId="5" r:id="R19a1fab227aa4ddd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05 读谱与声波" sheetId="6" r:id="R0ff0f47d3b92482a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06 随从" sheetId="7" r:id="Rf09ef960485e44ce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07 分界线表现" sheetId="8" r:id="R9c423461d0a24cd3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08 角色移动" sheetId="9" r:id="R66f3a1baf94440b6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09 BOSS 表现" sheetId="10" r:id="R1437e32e88c641df"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -53,7 +54,7 @@
       <x:name val="Microsoft YaHei"/>
     </x:font>
   </x:fonts>
-  <x:fills count="16">
+  <x:fills count="23">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -130,6 +131,41 @@
         <x:fgColor rgb="FFE7E8EA"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE7E8EA"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF0C2"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE7E8EA"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF3F5967"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF0C2"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE7E8EA"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF0C2"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="1">
     <x:border/>
@@ -137,7 +173,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="53">
+  <x:cellXfs count="71">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -273,6 +309,56 @@
       <x:alignment vertical="center"/>
     </x:xf>
     <x:xf numFmtId="200" fontId="1" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="205" fontId="1" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="205" fontId="1" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="1" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="1" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="205" fontId="1" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="1" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="205" fontId="1" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="205" fontId="1" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="1" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="205" fontId="1" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
   </x:cellXfs>
@@ -786,6 +872,209 @@
 </x:worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="13" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="13" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="15" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="30" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="72" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="32" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="40" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="58" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="2">
+      <x:c r="A2" s="2" t="str">
+        <x:v>BOSS 表现</x:v>
+      </x:c>
+      <x:c r="B2" s="1"/>
+      <x:c r="C2" s="1"/>
+      <x:c r="D2" s="1"/>
+      <x:c r="E2" s="1"/>
+      <x:c r="F2" s="1"/>
+      <x:c r="G2" s="1"/>
+      <x:c r="H2" s="1"/>
+      <x:c r="I2" s="1"/>
+      <x:c r="J2" s="1"/>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="1" t="str">
+        <x:v>修改黄色当前值，重新打开 BOSS 审看场景后生效。</x:v>
+      </x:c>
+      <x:c r="B3" s="1"/>
+      <x:c r="C3" s="1"/>
+      <x:c r="D3" s="1"/>
+      <x:c r="E3" s="1"/>
+      <x:c r="F3" s="1"/>
+      <x:c r="G3" s="1"/>
+      <x:c r="H3" s="1"/>
+      <x:c r="I3" s="1"/>
+      <x:c r="J3" s="1"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="1"/>
+      <x:c r="B4" s="1"/>
+      <x:c r="C4" s="1"/>
+      <x:c r="D4" s="1"/>
+      <x:c r="E4" s="1"/>
+      <x:c r="F4" s="1"/>
+      <x:c r="G4" s="1"/>
+      <x:c r="H4" s="1"/>
+      <x:c r="I4" s="1"/>
+      <x:c r="J4" s="1"/>
+    </x:row>
+    <x:row r="5" ht="30" customHeight="1">
+      <x:c r="A5" s="63" t="str">
+        <x:v>参数</x:v>
+      </x:c>
+      <x:c r="B5" s="63" t="str">
+        <x:v>当前值</x:v>
+      </x:c>
+      <x:c r="C5" s="63" t="str">
+        <x:v>原型默认</x:v>
+      </x:c>
+      <x:c r="D5" s="63" t="str">
+        <x:v>单位</x:v>
+      </x:c>
+      <x:c r="E5" s="63" t="str">
+        <x:v>建议试调区间</x:v>
+      </x:c>
+      <x:c r="F5" s="63" t="str">
+        <x:v>每次建议改动</x:v>
+      </x:c>
+      <x:c r="G5" s="63" t="str">
+        <x:v>作用与注意事项</x:v>
+      </x:c>
+      <x:c r="H5" s="63" t="str">
+        <x:v>配置对象</x:v>
+      </x:c>
+      <x:c r="I5" s="63" t="str">
+        <x:v>字段名</x:v>
+      </x:c>
+      <x:c r="J5" s="63" t="str">
+        <x:v>来源（Game 内）</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="46" customHeight="1">
+      <x:c r="A6" s="6" t="str">
+        <x:v>光效强度</x:v>
+      </x:c>
+      <x:c r="B6" s="21" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C6" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D6" s="6" t="str">
+        <x:v>倍</x:v>
+      </x:c>
+      <x:c r="E6" s="6" t="str">
+        <x:v>0～2</x:v>
+      </x:c>
+      <x:c r="F6" s="20" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="G6" s="8" t="str">
+        <x:v>调整光波、火焰、眼光及羊头裂光和白场。攻击不提亮手部，默认白场保持0.5秒。</x:v>
+      </x:c>
+      <x:c r="H6" s="6" t="str">
+        <x:v>boss</x:v>
+      </x:c>
+      <x:c r="I6" s="6" t="str">
+        <x:v>glow_strength</x:v>
+      </x:c>
+      <x:c r="J6" s="6" t="str">
+        <x:v>tools/boss_animation/boss_visual.gd</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="46" customHeight="1">
+      <x:c r="A7" s="6" t="str">
+        <x:v>光效范围</x:v>
+      </x:c>
+      <x:c r="B7" s="21" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C7" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D7" s="6" t="str">
+        <x:v>倍</x:v>
+      </x:c>
+      <x:c r="E7" s="6" t="str">
+        <x:v>0.5～1.5</x:v>
+      </x:c>
+      <x:c r="F7" s="20" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="G7" s="8" t="str">
+        <x:v>调整光波、火焰及羊头光束和骨片扩散范围，发射根部保持绑定。</x:v>
+      </x:c>
+      <x:c r="H7" s="6" t="str">
+        <x:v>boss</x:v>
+      </x:c>
+      <x:c r="I7" s="6" t="str">
+        <x:v>effect_scale</x:v>
+      </x:c>
+      <x:c r="J7" s="6" t="str">
+        <x:v>tools/boss_animation/boss_visual.gd</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="46" customHeight="1">
+      <x:c r="A8" s="6" t="str">
+        <x:v>碎片数量倍率</x:v>
+      </x:c>
+      <x:c r="B8" s="21" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C8" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D8" s="6" t="str">
+        <x:v>倍</x:v>
+      </x:c>
+      <x:c r="E8" s="6" t="str">
+        <x:v>0.25～2</x:v>
+      </x:c>
+      <x:c r="F8" s="20" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="G8" s="8" t="str">
+        <x:v>调整附属碎屑数量。羊头六片额眼表层与34块骨片固定，不改变动作时长。</x:v>
+      </x:c>
+      <x:c r="H8" s="6" t="str">
+        <x:v>boss</x:v>
+      </x:c>
+      <x:c r="I8" s="6" t="str">
+        <x:v>fragment_multiplier</x:v>
+      </x:c>
+      <x:c r="J8" s="6" t="str">
+        <x:v>tools/boss_animation/boss_visual.gd</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:dataValidations count="3">
+    <x:dataValidation type="decimal" operator="between" sqref="B6">
+      <x:formula1>0</x:formula1>
+      <x:formula2>2</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="decimal" operator="between" sqref="B7">
+      <x:formula1>0.5</x:formula1>
+      <x:formula2>1.5</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="decimal" operator="between" sqref="B8">
+      <x:formula1>0.25</x:formula1>
+      <x:formula2>2</x:formula2>
+    </x:dataValidation>
+  </x:dataValidations>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
@@ -3028,7 +3317,7 @@
       <x:c r="A7" s="6" t="str">
         <x:v>已停用：缓流周期</x:v>
       </x:c>
-      <x:c r="B7" s="51" t="n">
+      <x:c r="B7" s="66" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="C7" s="20" t="n">
@@ -3056,7 +3345,7 @@
       <x:c r="A8" s="6" t="str">
         <x:v>已停用：水带起伏</x:v>
       </x:c>
-      <x:c r="B8" s="51" t="n">
+      <x:c r="B8" s="66" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C8" s="20" t="n">
@@ -3084,7 +3373,7 @@
       <x:c r="A9" s="6" t="str">
         <x:v>已停用：大浪回卷</x:v>
       </x:c>
-      <x:c r="B9" s="51" t="n">
+      <x:c r="B9" s="66" t="n">
         <x:v>12</x:v>
       </x:c>
       <x:c r="C9" s="20" t="n">
@@ -3112,7 +3401,7 @@
       <x:c r="A10" s="6" t="str">
         <x:v>已停用：节拍回应</x:v>
       </x:c>
-      <x:c r="B10" s="52" t="n">
+      <x:c r="B10" s="67" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C10" s="10" t="n">
@@ -3140,7 +3429,7 @@
       <x:c r="A11" s="6" t="str">
         <x:v>已停用：节拍舒张幅度</x:v>
       </x:c>
-      <x:c r="B11" s="51" t="n">
+      <x:c r="B11" s="66" t="n">
         <x:v>1.2</x:v>
       </x:c>
       <x:c r="C11" s="20" t="n">
@@ -3166,9 +3455,9 @@
     </x:row>
     <x:row r="12" ht="46" customHeight="1">
       <x:c r="A12" s="6" t="str">
-        <x:v>大浪间隔</x:v>
-      </x:c>
-      <x:c r="B12" s="9" t="n">
+        <x:v>已停用：卷流接替间隔</x:v>
+      </x:c>
+      <x:c r="B12" s="67" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C12" s="10" t="n">
@@ -3184,23 +3473,19 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G12" s="8" t="str">
-        <x:v>每隔此数小节首拍拍落一对大浪；每道浪持续两小节。</x:v>
-      </x:c>
-      <x:c r="H12" s="6" t="str">
-        <x:v>boundary</x:v>
-      </x:c>
-      <x:c r="I12" s="6" t="str">
-        <x:v>bar_interval</x:v>
-      </x:c>
+        <x:v>每隔此数小节接入一对新水臂；每道水臂持续两个接替间隔。</x:v>
+      </x:c>
+      <x:c r="H12" s="6" t="str"/>
+      <x:c r="I12" s="6" t="str"/>
       <x:c r="J12" s="6" t="str">
         <x:v>src/content/resources/boundary_motion_style.gd</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="46" customHeight="1">
       <x:c r="A13" s="6" t="str">
-        <x:v>大浪高度</x:v>
-      </x:c>
-      <x:c r="B13" s="21" t="n">
+        <x:v>已停用：大浪高度</x:v>
+      </x:c>
+      <x:c r="B13" s="66" t="n">
         <x:v>165</x:v>
       </x:c>
       <x:c r="C13" s="20" t="n">
@@ -3218,21 +3503,17 @@
       <x:c r="G13" s="8" t="str">
         <x:v>最高伸顶姿势的高度；修改后检查判定圈周围留白。</x:v>
       </x:c>
-      <x:c r="H13" s="6" t="str">
-        <x:v>boundary</x:v>
-      </x:c>
-      <x:c r="I13" s="6" t="str">
-        <x:v>wave_height_px</x:v>
-      </x:c>
+      <x:c r="H13" s="6" t="str"/>
+      <x:c r="I13" s="6" t="str"/>
       <x:c r="J13" s="6" t="str">
         <x:v>src/content/resources/boundary_motion_style.gd</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="46" customHeight="1">
       <x:c r="A14" s="6" t="str">
-        <x:v>浪身推进</x:v>
-      </x:c>
-      <x:c r="B14" s="21" t="n">
+        <x:v>已停用：浪身推进</x:v>
+      </x:c>
+      <x:c r="B14" s="66" t="n">
         <x:v>190</x:v>
       </x:c>
       <x:c r="C14" s="20" t="n">
@@ -3250,21 +3531,17 @@
       <x:c r="G14" s="8" t="str">
         <x:v>从低水脊到触水的前进距离；水沫随后再前滑约 120 px。</x:v>
       </x:c>
-      <x:c r="H14" s="6" t="str">
-        <x:v>boundary</x:v>
-      </x:c>
-      <x:c r="I14" s="6" t="str">
-        <x:v>advance_px</x:v>
-      </x:c>
+      <x:c r="H14" s="6" t="str"/>
+      <x:c r="I14" s="6" t="str"/>
       <x:c r="J14" s="6" t="str">
         <x:v>src/content/resources/boundary_motion_style.gd</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="46" customHeight="1">
       <x:c r="A15" s="6" t="str">
-        <x:v>翻卷行程</x:v>
-      </x:c>
-      <x:c r="B15" s="21" t="n">
+        <x:v>已停用：翻卷行程</x:v>
+      </x:c>
+      <x:c r="B15" s="66" t="n">
         <x:v>90</x:v>
       </x:c>
       <x:c r="C15" s="20" t="n">
@@ -3282,21 +3559,17 @@
       <x:c r="G15" s="8" t="str">
         <x:v>控制浪唇横向舒展与翻送尺度，浪高独立配置。</x:v>
       </x:c>
-      <x:c r="H15" s="6" t="str">
-        <x:v>boundary</x:v>
-      </x:c>
-      <x:c r="I15" s="6" t="str">
-        <x:v>curl_travel_px</x:v>
-      </x:c>
+      <x:c r="H15" s="6" t="str"/>
+      <x:c r="I15" s="6" t="str"/>
       <x:c r="J15" s="6" t="str">
         <x:v>src/content/resources/boundary_motion_style.gd</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="46" customHeight="1">
       <x:c r="A16" s="6" t="str">
-        <x:v>白沫强度</x:v>
-      </x:c>
-      <x:c r="B16" s="11" t="n">
+        <x:v>已停用：拍落白沫强度</x:v>
+      </x:c>
+      <x:c r="B16" s="68" t="n">
         <x:v>0.9</x:v>
       </x:c>
       <x:c r="C16" s="12" t="n">
@@ -3314,12 +3587,8 @@
       <x:c r="G16" s="8" t="str">
         <x:v>只控制拍落后白沫和细水线的不透明度。</x:v>
       </x:c>
-      <x:c r="H16" s="6" t="str">
-        <x:v>boundary</x:v>
-      </x:c>
-      <x:c r="I16" s="6" t="str">
-        <x:v>foam_strength</x:v>
-      </x:c>
+      <x:c r="H16" s="6" t="str"/>
+      <x:c r="I16" s="6" t="str"/>
       <x:c r="J16" s="6" t="str">
         <x:v>src/content/resources/boundary_motion_style.gd</x:v>
       </x:c>
@@ -3452,8 +3721,224 @@
         <x:v>src/content/resources/boundary_motion_style.gd</x:v>
       </x:c>
     </x:row>
+    <x:row r="21" ht="46" customHeight="1">
+      <x:c r="A21" s="6" t="str">
+        <x:v>已停用：漩涡外半径</x:v>
+      </x:c>
+      <x:c r="B21" s="66" t="n">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="C21" s="20" t="n">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="D21" s="6" t="str">
+        <x:v>设计 px</x:v>
+      </x:c>
+      <x:c r="E21" s="6" t="str">
+        <x:v>160～180</x:v>
+      </x:c>
+      <x:c r="F21" s="10" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G21" s="8" t="str">
+        <x:v>中央卷臂的外侧尺度；加宽的水坡接入两侧底带。</x:v>
+      </x:c>
+      <x:c r="H21" s="6" t="str"/>
+      <x:c r="I21" s="6" t="str"/>
+      <x:c r="J21" s="6" t="str">
+        <x:v>src/content/resources/boundary_motion_style.gd</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="46" customHeight="1">
+      <x:c r="A22" s="6" t="str">
+        <x:v>漩涡内半径</x:v>
+      </x:c>
+      <x:c r="B22" s="21" t="n">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C22" s="20" t="n">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="D22" s="6" t="str">
+        <x:v>设计 px</x:v>
+      </x:c>
+      <x:c r="E22" s="6" t="str">
+        <x:v>88～100</x:v>
+      </x:c>
+      <x:c r="F22" s="10" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G22" s="8" t="str">
+        <x:v>中央留白的基准尺度；整体弧面向外调整，不裁切水体。</x:v>
+      </x:c>
+      <x:c r="H22" s="6" t="str">
+        <x:v>boundary</x:v>
+      </x:c>
+      <x:c r="I22" s="6" t="str">
+        <x:v>vortex_inner_radius_px</x:v>
+      </x:c>
+      <x:c r="J22" s="6" t="str">
+        <x:v>src/content/resources/boundary_motion_style.gd</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="46" customHeight="1">
+      <x:c r="A23" s="6" t="str">
+        <x:v>已停用：卷入角度</x:v>
+      </x:c>
+      <x:c r="B23" s="66" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="C23" s="20" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="D23" s="6" t="str">
+        <x:v>度</x:v>
+      </x:c>
+      <x:c r="E23" s="6" t="str">
+        <x:v>220～250</x:v>
+      </x:c>
+      <x:c r="F23" s="10" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G23" s="8" t="str">
+        <x:v>调整卷臂的弯转；240°对应补绘的原画姿态。</x:v>
+      </x:c>
+      <x:c r="H23" s="6" t="str"/>
+      <x:c r="I23" s="6" t="str"/>
+      <x:c r="J23" s="6" t="str">
+        <x:v>src/content/resources/boundary_motion_style.gd</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="46" customHeight="1">
+      <x:c r="A24" s="6" t="str">
+        <x:v>浪身宽度</x:v>
+      </x:c>
+      <x:c r="B24" s="21" t="n">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="C24" s="20" t="n">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="D24" s="6" t="str">
+        <x:v>设计 px</x:v>
+      </x:c>
+      <x:c r="E24" s="6" t="str">
+        <x:v>100～130</x:v>
+      </x:c>
+      <x:c r="F24" s="10" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G24" s="8" t="str">
+        <x:v>向浪身外缘增加厚度；入口下缘保持平顺上行。</x:v>
+      </x:c>
+      <x:c r="H24" s="6" t="str">
+        <x:v>boundary</x:v>
+      </x:c>
+      <x:c r="I24" s="6" t="str">
+        <x:v>vortex_width_px</x:v>
+      </x:c>
+      <x:c r="J24" s="6" t="str">
+        <x:v>src/content/resources/boundary_motion_style.gd</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="46" customHeight="1">
+      <x:c r="A25" s="6" t="str">
+        <x:v>细沫强度</x:v>
+      </x:c>
+      <x:c r="B25" s="11" t="n">
+        <x:v>0.65</x:v>
+      </x:c>
+      <x:c r="C25" s="12" t="n">
+        <x:v>0.65</x:v>
+      </x:c>
+      <x:c r="D25" s="6" t="str">
+        <x:v>比例</x:v>
+      </x:c>
+      <x:c r="E25" s="6" t="str">
+        <x:v>50%～75%</x:v>
+      </x:c>
+      <x:c r="F25" s="12" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="G25" s="8" t="str">
+        <x:v>沿卷流前进的骨白细水纹混合强度。</x:v>
+      </x:c>
+      <x:c r="H25" s="6" t="str">
+        <x:v>boundary</x:v>
+      </x:c>
+      <x:c r="I25" s="6" t="str">
+        <x:v>vortex_foam_strength</x:v>
+      </x:c>
+      <x:c r="J25" s="6" t="str">
+        <x:v>src/content/resources/boundary_motion_style.gd</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="46" customHeight="1">
+      <x:c r="A26" s="6" t="str">
+        <x:v>卷流速度</x:v>
+      </x:c>
+      <x:c r="B26" s="70" t="n">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="C26" s="20" t="n">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="D26" s="6" t="str">
+        <x:v>设计 px/s</x:v>
+      </x:c>
+      <x:c r="E26" s="6" t="str">
+        <x:v>80～120</x:v>
+      </x:c>
+      <x:c r="F26" s="10" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G26" s="8" t="str">
+        <x:v>水纹沿厚浪弧线连续前进的速度；浪缘略快，抵达尖端逐渐消散。</x:v>
+      </x:c>
+      <x:c r="H26" s="6" t="str">
+        <x:v>boundary</x:v>
+      </x:c>
+      <x:c r="I26" s="6" t="str">
+        <x:v>vortex_flow_speed_px_sec</x:v>
+      </x:c>
+      <x:c r="J26" s="6" t="str">
+        <x:v>src/content/resources/boundary_motion_style.gd</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="46" customHeight="1">
+      <x:c r="A27" s="6" t="str">
+        <x:v>每拍推进</x:v>
+      </x:c>
+      <x:c r="B27" s="70" t="n">
+        <x:v>1.25</x:v>
+      </x:c>
+      <x:c r="C27" s="20" t="n">
+        <x:v>1.25</x:v>
+      </x:c>
+      <x:c r="D27" s="6" t="str">
+        <x:v>设计 px/拍</x:v>
+      </x:c>
+      <x:c r="E27" s="6" t="str">
+        <x:v>0～2</x:v>
+      </x:c>
+      <x:c r="F27" s="20" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="G27" s="8" t="str">
+        <x:v>每拍前 0.4 拍柔和增加的路程；0 关闭提速，基础卷流继续。</x:v>
+      </x:c>
+      <x:c r="H27" s="6" t="str">
+        <x:v>boundary</x:v>
+      </x:c>
+      <x:c r="I27" s="6" t="str">
+        <x:v>vortex_beat_push_px</x:v>
+      </x:c>
+      <x:c r="J27" s="6" t="str">
+        <x:v>src/content/resources/boundary_motion_style.gd</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:dataValidations count="15">
+  <x:dataValidations count="22">
     <x:dataValidation type="whole" operator="between" sqref="B6">
       <x:formula1>0</x:formula1>
       <x:formula2>1</x:formula2>
@@ -3513,6 +3998,34 @@
     <x:dataValidation type="decimal" operator="between" sqref="B20">
       <x:formula1>0</x:formula1>
       <x:formula2>0.4</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="decimal" operator="between" sqref="B21">
+      <x:formula1>145</x:formula1>
+      <x:formula2>200</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="decimal" operator="between" sqref="B22">
+      <x:formula1>80</x:formula1>
+      <x:formula2>110</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="decimal" operator="between" sqref="B23">
+      <x:formula1>180</x:formula1>
+      <x:formula2>270</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="decimal" operator="between" sqref="B24">
+      <x:formula1>80</x:formula1>
+      <x:formula2>150</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="decimal" operator="between" sqref="B25">
+      <x:formula1>0</x:formula1>
+      <x:formula2>1</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="decimal" operator="between" sqref="B26">
+      <x:formula1>0</x:formula1>
+      <x:formula2>180</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="decimal" operator="between" sqref="B27">
+      <x:formula1>0</x:formula1>
+      <x:formula2>3</x:formula2>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/outputs/planning/策划参数.xlsx
+++ b/outputs/planning/策划参数.xlsx
@@ -2,16 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用与量级" sheetId="1" r:id="Raad4d06ba1034db4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01 判定与容错" sheetId="2" r:id="R517b9f7929154c5e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02 魂火与惩罚" sheetId="3" r:id="Rfda77c3f4e3b42c9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03 调频" sheetId="4" r:id="R27630d1f84a5484f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04 计分" sheetId="5" r:id="R19a1fab227aa4ddd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05 读谱与声波" sheetId="6" r:id="R0ff0f47d3b92482a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06 随从" sheetId="7" r:id="Rf09ef960485e44ce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07 分界线表现" sheetId="8" r:id="R9c423461d0a24cd3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08 角色移动" sheetId="9" r:id="R66f3a1baf94440b6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09 BOSS 表现" sheetId="10" r:id="R1437e32e88c641df"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用与量级" sheetId="1" r:id="Rec67bc50862a45f4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01 判定与容错" sheetId="2" r:id="R448535638567437f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02 魂火与惩罚" sheetId="3" r:id="Rf82cca8fdb334f97"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03 调频" sheetId="4" r:id="Rcd018f363c9c46d3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04 计分" sheetId="5" r:id="R4f23f21484b649e9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05 读谱与声波" sheetId="6" r:id="Rcd6a49640c0344b9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06 随从" sheetId="7" r:id="R313bb3d6aebd4f8d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07 分界线表现" sheetId="8" r:id="R49c14e9602b14ea5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08 角色移动" sheetId="9" r:id="R4143b1a2650f4a0b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09 BOSS 表现" sheetId="10" r:id="Rb7b1e0ed41694baf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10 UI 火框" sheetId="11" r:id="Ra0c4c7f17ada4125"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -54,7 +55,7 @@
       <x:name val="Microsoft YaHei"/>
     </x:font>
   </x:fonts>
-  <x:fills count="23">
+  <x:fills count="25">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -166,6 +167,16 @@
         <x:fgColor rgb="FFFFF0C2"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF3F5967"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF0C2"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="1">
     <x:border/>
@@ -173,7 +184,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="71">
+  <x:cellXfs count="75">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -359,6 +370,14 @@
       <x:alignment vertical="center"/>
     </x:xf>
     <x:xf numFmtId="205" fontId="1" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="24" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="205" fontId="1" fillId="24" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
   </x:cellXfs>
@@ -1075,6 +1094,209 @@
 </x:worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="13" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="13" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="15" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="30" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="72" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="32" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="40" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="58" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="2">
+      <x:c r="A2" s="2" t="str">
+        <x:v>UI 火框</x:v>
+      </x:c>
+      <x:c r="B2" s="1"/>
+      <x:c r="C2" s="1"/>
+      <x:c r="D2" s="1"/>
+      <x:c r="E2" s="1"/>
+      <x:c r="F2" s="1"/>
+      <x:c r="G2" s="1"/>
+      <x:c r="H2" s="1"/>
+      <x:c r="I2" s="1"/>
+      <x:c r="J2" s="1"/>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="1" t="str">
+        <x:v>修改黄色当前值，重新打开 UI 火框审看场景后生效；本轮尚未替换正式界面。</x:v>
+      </x:c>
+      <x:c r="B3" s="1"/>
+      <x:c r="C3" s="1"/>
+      <x:c r="D3" s="1"/>
+      <x:c r="E3" s="1"/>
+      <x:c r="F3" s="1"/>
+      <x:c r="G3" s="1"/>
+      <x:c r="H3" s="1"/>
+      <x:c r="I3" s="1"/>
+      <x:c r="J3" s="1"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="1"/>
+      <x:c r="B4" s="1"/>
+      <x:c r="C4" s="1"/>
+      <x:c r="D4" s="1"/>
+      <x:c r="E4" s="1"/>
+      <x:c r="F4" s="1"/>
+      <x:c r="G4" s="1"/>
+      <x:c r="H4" s="1"/>
+      <x:c r="I4" s="1"/>
+      <x:c r="J4" s="1"/>
+    </x:row>
+    <x:row r="5" ht="30" customHeight="1">
+      <x:c r="A5" s="72" t="str">
+        <x:v>参数</x:v>
+      </x:c>
+      <x:c r="B5" s="72" t="str">
+        <x:v>当前值</x:v>
+      </x:c>
+      <x:c r="C5" s="72" t="str">
+        <x:v>原型默认</x:v>
+      </x:c>
+      <x:c r="D5" s="72" t="str">
+        <x:v>单位</x:v>
+      </x:c>
+      <x:c r="E5" s="72" t="str">
+        <x:v>建议试调区间</x:v>
+      </x:c>
+      <x:c r="F5" s="72" t="str">
+        <x:v>每次建议改动</x:v>
+      </x:c>
+      <x:c r="G5" s="72" t="str">
+        <x:v>作用与注意事项</x:v>
+      </x:c>
+      <x:c r="H5" s="72" t="str">
+        <x:v>配置对象</x:v>
+      </x:c>
+      <x:c r="I5" s="72" t="str">
+        <x:v>字段名</x:v>
+      </x:c>
+      <x:c r="J5" s="72" t="str">
+        <x:v>来源（Game 内）</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="46" customHeight="1">
+      <x:c r="A6" s="6" t="str">
+        <x:v>火势高度</x:v>
+      </x:c>
+      <x:c r="B6" s="21" t="n">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C6" s="20" t="n">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="D6" s="6" t="str">
+        <x:v>设计 px</x:v>
+      </x:c>
+      <x:c r="E6" s="6" t="str">
+        <x:v>24～72</x:v>
+      </x:c>
+      <x:c r="F6" s="10" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G6" s="8" t="str">
+        <x:v>控制火舌的基准高度；根部固定，焰身持续上窜，少数火簇较大、其余细短。调节时环带透明边距同步更新，不拉伸整张原图。</x:v>
+      </x:c>
+      <x:c r="H6" s="6" t="str">
+        <x:v>ui_flame</x:v>
+      </x:c>
+      <x:c r="I6" s="6" t="str">
+        <x:v>flame_height</x:v>
+      </x:c>
+      <x:c r="J6" s="6" t="str">
+        <x:v>src/presentation/ui/flame_frame_visual.gd</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="46" customHeight="1">
+      <x:c r="A7" s="6" t="str">
+        <x:v>燃烧速度</x:v>
+      </x:c>
+      <x:c r="B7" s="21" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C7" s="20" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="D7" s="6" t="str">
+        <x:v>设计 px/s</x:v>
+      </x:c>
+      <x:c r="E7" s="6" t="str">
+        <x:v>0～180</x:v>
+      </x:c>
+      <x:c r="F7" s="10" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G7" s="8" t="str">
+        <x:v>控制焰身上窜、卷动与尖端消退的时间速度；0冻结，红蓝共用同一运动规律。</x:v>
+      </x:c>
+      <x:c r="H7" s="6" t="str">
+        <x:v>ui_flame</x:v>
+      </x:c>
+      <x:c r="I7" s="6" t="str">
+        <x:v>speed</x:v>
+      </x:c>
+      <x:c r="J7" s="6" t="str">
+        <x:v>src/presentation/ui/flame_frame_visual.gd</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="46" customHeight="1">
+      <x:c r="A8" s="6" t="str">
+        <x:v>柔晕强度</x:v>
+      </x:c>
+      <x:c r="B8" s="21" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C8" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D8" s="6" t="str">
+        <x:v>倍</x:v>
+      </x:c>
+      <x:c r="E8" s="6" t="str">
+        <x:v>0～2</x:v>
+      </x:c>
+      <x:c r="F8" s="20" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="G8" s="8" t="str">
+        <x:v>只调节局部外晕及八个附属火尖；0保留主要火焰，不改变文字或背景亮度。</x:v>
+      </x:c>
+      <x:c r="H8" s="6" t="str">
+        <x:v>ui_flame</x:v>
+      </x:c>
+      <x:c r="I8" s="6" t="str">
+        <x:v>glow_strength</x:v>
+      </x:c>
+      <x:c r="J8" s="6" t="str">
+        <x:v>src/presentation/ui/flame_frame_visual.gd</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:dataValidations count="3">
+    <x:dataValidation type="decimal" operator="between" sqref="B6">
+      <x:formula1>24</x:formula1>
+      <x:formula2>72</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="decimal" operator="between" sqref="B7">
+      <x:formula1>0</x:formula1>
+      <x:formula2>180</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="decimal" operator="between" sqref="B8">
+      <x:formula1>0</x:formula1>
+      <x:formula2>2</x:formula2>
+    </x:dataValidation>
+  </x:dataValidations>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
@@ -1311,7 +1533,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="G10" s="8" t="str">
-        <x:v>短暂松开允许续接；超过宽限失败，尾点自动完成，无松尾判定。</x:v>
+        <x:v>短暂松开可续接；超时失败并淡出关联调频条。尾点自动完成，无松尾判定。</x:v>
       </x:c>
       <x:c r="H10" s="6" t="str">
         <x:v>rules</x:v>
@@ -2193,7 +2415,7 @@
         <x:v>0.01</x:v>
       </x:c>
       <x:c r="G17" s="8" t="str">
-        <x:v>最低成功比例；低于此值或松开对应钟记 Miss。滑条不扣血，关联 Ghost 失败才扣血。</x:v>
+        <x:v>最低成功比例；低于此值或松开记 Miss。关联 Hold 失败后滑条淡出，仍按原时刻结算；仅 Ghost 扣血。</x:v>
       </x:c>
       <x:c r="H17" s="6" t="str">
         <x:v>rules</x:v>

--- a/outputs/planning/策划参数.xlsx
+++ b/outputs/planning/策划参数.xlsx
@@ -2,17 +2,20 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用与量级" sheetId="1" r:id="Rec67bc50862a45f4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01 判定与容错" sheetId="2" r:id="R448535638567437f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02 魂火与惩罚" sheetId="3" r:id="Rf82cca8fdb334f97"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03 调频" sheetId="4" r:id="Rcd018f363c9c46d3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04 计分" sheetId="5" r:id="R4f23f21484b649e9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05 读谱与声波" sheetId="6" r:id="Rcd6a49640c0344b9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06 随从" sheetId="7" r:id="R313bb3d6aebd4f8d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07 分界线表现" sheetId="8" r:id="R49c14e9602b14ea5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08 角色移动" sheetId="9" r:id="R4143b1a2650f4a0b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09 BOSS 表现" sheetId="10" r:id="Rb7b1e0ed41694baf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10 UI 火框" sheetId="11" r:id="Ra0c4c7f17ada4125"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用与量级" sheetId="1" r:id="Rffc3a45d618d4cbb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01 判定与容错" sheetId="2" r:id="Re46629753cf844aa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02 魂火与惩罚" sheetId="3" r:id="Rfcfeca461b234a98"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03 调频" sheetId="4" r:id="Rc227d69b65594de4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04 计分" sheetId="5" r:id="R27e56c37caeb4c29"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05 读谱与声波" sheetId="6" r:id="Rd62456e3c7e94ef0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06 随从" sheetId="7" r:id="R4275c21e90114ba2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07 分界线表现" sheetId="8" r:id="R18e784fca0da409d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08 角色移动" sheetId="9" r:id="Rb26277c02d554bfa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09 BOSS 表现" sheetId="10" r:id="Re72c04aedc13426d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10 UI 火框" sheetId="11" r:id="Rda7a750d22b94e54"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11 关卡奖励" sheetId="12" r:id="R73895b002b544f11"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12 开屏引导" sheetId="13" r:id="R8c433707ea804329"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13 判定表现" sheetId="14" r:id="R27e3beafddf24540"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -55,7 +58,7 @@
       <x:name val="Microsoft YaHei"/>
     </x:font>
   </x:fonts>
-  <x:fills count="25">
+  <x:fills count="36">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -177,6 +180,61 @@
         <x:fgColor rgb="FFFFF0C2"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF0C2"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF0C2"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE7E8EA"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF3F5967"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF0C2"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE7E8EA"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF3F5967"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF0C2"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF0C2"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF3F5967"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF0C2"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="1">
     <x:border/>
@@ -184,7 +242,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="75">
+  <x:cellXfs count="102">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -378,6 +436,75 @@
       <x:alignment vertical="center"/>
     </x:xf>
     <x:xf numFmtId="205" fontId="1" fillId="24" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="25" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="205" fontId="1" fillId="25" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="26" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="205" fontId="1" fillId="26" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="205" fontId="1" fillId="27" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="27" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="1" fillId="27" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="28" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="28" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="29" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="206" fontId="1" fillId="29" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="29" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="205" fontId="1" fillId="30" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="30" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="1" fillId="30" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="31" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="31" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="32" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="205" fontId="1" fillId="32" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="205" fontId="1" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="205" fontId="1" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="1" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="206" fontId="1" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
   </x:cellXfs>
@@ -794,7 +921,7 @@
     </x:row>
     <x:row r="20" ht="30" customHeight="1">
       <x:c r="A20" s="1" t="str">
-        <x:v>羊头仔基础：每组 Tap 伤害（点）</x:v>
+        <x:v>鬼金羊基础：每组 Tap 伤害（点）</x:v>
       </x:c>
       <x:c r="B20" s="1" t="n">
         <x:f>ROUND('02 魂火与惩罚'!B7*(1-'06 随从'!B8),0)</x:f>
@@ -1075,8 +1202,104 @@
         <x:v>tools/boss_animation/boss_visual.gd</x:v>
       </x:c>
     </x:row>
+    <x:row r="9" ht="46" customHeight="1">
+      <x:c r="A9" s="6" t="str">
+        <x:v>BOSS 血量比例</x:v>
+      </x:c>
+      <x:c r="B9" s="95" t="n">
+        <x:v>0.8</x:v>
+      </x:c>
+      <x:c r="C9" s="20" t="n">
+        <x:v>0.8</x:v>
+      </x:c>
+      <x:c r="D9" s="6" t="str">
+        <x:v>倍</x:v>
+      </x:c>
+      <x:c r="E9" s="6" t="str">
+        <x:v>0.05～2</x:v>
+      </x:c>
+      <x:c r="F9" s="20" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="G9" s="8" t="str">
+        <x:v>最大血量相对所属音符理论总伤害；零血先破防，最后一波结束后死亡。</x:v>
+      </x:c>
+      <x:c r="H9" s="6" t="str">
+        <x:v>boss</x:v>
+      </x:c>
+      <x:c r="I9" s="6" t="str">
+        <x:v>health_ratio</x:v>
+      </x:c>
+      <x:c r="J9" s="6" t="str">
+        <x:v>src/runtime/director/level_boss_compiler.gd</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="46" customHeight="1">
+      <x:c r="A10" s="6" t="str">
+        <x:v>BOSS 巡航速度</x:v>
+      </x:c>
+      <x:c r="B10" s="95" t="n">
+        <x:v>600</x:v>
+      </x:c>
+      <x:c r="C10" s="20" t="n">
+        <x:v>600</x:v>
+      </x:c>
+      <x:c r="D10" s="6" t="str">
+        <x:v>设计像素/秒</x:v>
+      </x:c>
+      <x:c r="E10" s="6" t="str">
+        <x:v>100～3000</x:v>
+      </x:c>
+      <x:c r="F10" s="10" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G10" s="8" t="str">
+        <x:v>根据曲线弧长反推提前发射时间，不改变判定拍点；对象及绑定可以覆盖。</x:v>
+      </x:c>
+      <x:c r="H10" s="6" t="str">
+        <x:v>boss</x:v>
+      </x:c>
+      <x:c r="I10" s="6" t="str">
+        <x:v>flight_speed</x:v>
+      </x:c>
+      <x:c r="J10" s="6" t="str">
+        <x:v>src/runtime/director/level_boss_compiler.gd</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="46" customHeight="1">
+      <x:c r="A11" s="6" t="str">
+        <x:v>BOSS 散射半角</x:v>
+      </x:c>
+      <x:c r="B11" s="95" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C11" s="20" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D11" s="6" t="str">
+        <x:v>度</x:v>
+      </x:c>
+      <x:c r="E11" s="6" t="str">
+        <x:v>0～60</x:v>
+      </x:c>
+      <x:c r="F11" s="10" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G11" s="8" t="str">
+        <x:v>对应侧出手方向的随机半角；稳定音符 ID 决定结果，后段平滑贴回原路线。</x:v>
+      </x:c>
+      <x:c r="H11" s="6" t="str">
+        <x:v>boss</x:v>
+      </x:c>
+      <x:c r="I11" s="6" t="str">
+        <x:v>spread_deg</x:v>
+      </x:c>
+      <x:c r="J11" s="6" t="str">
+        <x:v>src/runtime/director/level_boss_compiler.gd</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:dataValidations count="3">
+  <x:dataValidations count="6">
     <x:dataValidation type="decimal" operator="between" sqref="B6">
       <x:formula1>0</x:formula1>
       <x:formula2>2</x:formula2>
@@ -1088,6 +1311,18 @@
     <x:dataValidation type="decimal" operator="between" sqref="B8">
       <x:formula1>0.25</x:formula1>
       <x:formula2>2</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="decimal" operator="between" sqref="B9">
+      <x:formula1>0.05</x:formula1>
+      <x:formula2>2</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="decimal" operator="between" sqref="B10">
+      <x:formula1>100</x:formula1>
+      <x:formula2>3000</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="decimal" operator="between" sqref="B11">
+      <x:formula1>0</x:formula1>
+      <x:formula2>60</x:formula2>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1297,6 +1532,1015 @@
 </x:worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="20" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="20" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="15" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="30" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="72" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="32" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="40" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="58" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="2">
+      <x:c r="A2" s="2" t="str">
+        <x:v>关卡奖励</x:v>
+      </x:c>
+      <x:c r="B2" s="1"/>
+      <x:c r="C2" s="1"/>
+      <x:c r="D2" s="1"/>
+      <x:c r="E2" s="1"/>
+      <x:c r="F2" s="1"/>
+      <x:c r="G2" s="1"/>
+      <x:c r="H2" s="1"/>
+      <x:c r="I2" s="1"/>
+      <x:c r="J2" s="1"/>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="1" t="str">
+        <x:v>修改黄色当前值，下次正式装载生效。玄同收服、至臻进阶；不会撤回既有奖励。</x:v>
+      </x:c>
+      <x:c r="B3" s="1"/>
+      <x:c r="C3" s="1"/>
+      <x:c r="D3" s="1"/>
+      <x:c r="E3" s="1"/>
+      <x:c r="F3" s="1"/>
+      <x:c r="G3" s="1"/>
+      <x:c r="H3" s="1"/>
+      <x:c r="I3" s="1"/>
+      <x:c r="J3" s="1"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="1"/>
+      <x:c r="B4" s="1"/>
+      <x:c r="C4" s="1"/>
+      <x:c r="D4" s="1"/>
+      <x:c r="E4" s="1"/>
+      <x:c r="F4" s="1"/>
+      <x:c r="G4" s="1"/>
+      <x:c r="H4" s="1"/>
+      <x:c r="I4" s="1"/>
+      <x:c r="J4" s="1"/>
+    </x:row>
+    <x:row r="5" ht="30" customHeight="1">
+      <x:c r="A5" s="83" t="str">
+        <x:v>参数</x:v>
+      </x:c>
+      <x:c r="B5" s="83" t="str">
+        <x:v>当前值</x:v>
+      </x:c>
+      <x:c r="C5" s="83" t="str">
+        <x:v>原型默认</x:v>
+      </x:c>
+      <x:c r="D5" s="83" t="str">
+        <x:v>单位</x:v>
+      </x:c>
+      <x:c r="E5" s="83" t="str">
+        <x:v>建议试调区间</x:v>
+      </x:c>
+      <x:c r="F5" s="83" t="str">
+        <x:v>每次建议改动</x:v>
+      </x:c>
+      <x:c r="G5" s="83" t="str">
+        <x:v>作用与注意事项</x:v>
+      </x:c>
+      <x:c r="H5" s="83" t="str">
+        <x:v>配置对象</x:v>
+      </x:c>
+      <x:c r="I5" s="83" t="str">
+        <x:v>字段名</x:v>
+      </x:c>
+      <x:c r="J5" s="83" t="str">
+        <x:v>来源（Game 内）</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="46" customHeight="1">
+      <x:c r="A6" s="6" t="str">
+        <x:v>女土蝠 · 下一关</x:v>
+      </x:c>
+      <x:c r="B6" s="50" t="str">
+        <x:v>s07</x:v>
+      </x:c>
+      <x:c r="C6" s="47" t="str">
+        <x:v>s07</x:v>
+      </x:c>
+      <x:c r="D6" s="6" t="str">
+        <x:v>关卡 ID</x:v>
+      </x:c>
+      <x:c r="E6" s="6" t="str">
+        <x:v>已登记关卡 ID / 留空</x:v>
+      </x:c>
+      <x:c r="F6" s="10" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G6" s="8" t="str">
+        <x:v>通关后解锁并提供下一关入口。填写关卡稳定 ID；留空表示末关。仅正式关卡使用。</x:v>
+      </x:c>
+      <x:c r="H6" s="6" t="str">
+        <x:v>reward:tutorial2</x:v>
+      </x:c>
+      <x:c r="I6" s="6" t="str">
+        <x:v>next_stage_id</x:v>
+      </x:c>
+      <x:c r="J6" s="6" t="str">
+        <x:v>content/stages/tutorial2/reward.tres</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="46" customHeight="1">
+      <x:c r="A7" s="6" t="str">
+        <x:v>女土蝠 · 玄同收服</x:v>
+      </x:c>
+      <x:c r="B7" s="9" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C7" s="10" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D7" s="6" t="str">
+        <x:v>开关</x:v>
+      </x:c>
+      <x:c r="E7" s="6" t="str">
+        <x:v>0 / 1</x:v>
+      </x:c>
+      <x:c r="F7" s="10" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G7" s="8" t="str">
+        <x:v>玄同授予本关对应随从的基础形态。0 关闭，1 开启；不撤回已经获得的随从。</x:v>
+      </x:c>
+      <x:c r="H7" s="6" t="str">
+        <x:v>reward:tutorial2</x:v>
+      </x:c>
+      <x:c r="I7" s="6" t="str">
+        <x:v>fc_grants_base_pet</x:v>
+      </x:c>
+      <x:c r="J7" s="6" t="str">
+        <x:v>content/stages/tutorial2/reward.tres</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="46" customHeight="1">
+      <x:c r="A8" s="6" t="str">
+        <x:v>女土蝠 · 至臻进阶</x:v>
+      </x:c>
+      <x:c r="B8" s="9" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C8" s="10" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D8" s="6" t="str">
+        <x:v>开关</x:v>
+      </x:c>
+      <x:c r="E8" s="6" t="str">
+        <x:v>0 / 1</x:v>
+      </x:c>
+      <x:c r="F8" s="10" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G8" s="8" t="str">
+        <x:v>至臻授予本关对应随从的进阶形态，并保证已收服。0 关闭，1 开启。</x:v>
+      </x:c>
+      <x:c r="H8" s="6" t="str">
+        <x:v>reward:tutorial2</x:v>
+      </x:c>
+      <x:c r="I8" s="6" t="str">
+        <x:v>ap_grants_advanced_pet</x:v>
+      </x:c>
+      <x:c r="J8" s="6" t="str">
+        <x:v>content/stages/tutorial2/reward.tres</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="46" customHeight="1">
+      <x:c r="A9" s="6" t="str">
+        <x:v>翼火蛇 · 下一关</x:v>
+      </x:c>
+      <x:c r="B9" s="50" t="str">
+        <x:v>s08</x:v>
+      </x:c>
+      <x:c r="C9" s="47" t="str">
+        <x:v>s08</x:v>
+      </x:c>
+      <x:c r="D9" s="6" t="str">
+        <x:v>关卡 ID</x:v>
+      </x:c>
+      <x:c r="E9" s="6" t="str">
+        <x:v>已登记关卡 ID / 留空</x:v>
+      </x:c>
+      <x:c r="F9" s="10" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G9" s="8" t="str">
+        <x:v>通关后解锁并提供下一关入口。填写关卡稳定 ID；留空表示末关。仅正式关卡使用。</x:v>
+      </x:c>
+      <x:c r="H9" s="6" t="str">
+        <x:v>reward:s07</x:v>
+      </x:c>
+      <x:c r="I9" s="6" t="str">
+        <x:v>next_stage_id</x:v>
+      </x:c>
+      <x:c r="J9" s="6" t="str">
+        <x:v>content/stages/s07/reward_definition.tres</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="46" customHeight="1">
+      <x:c r="A10" s="6" t="str">
+        <x:v>翼火蛇 · 玄同收服</x:v>
+      </x:c>
+      <x:c r="B10" s="9" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C10" s="10" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D10" s="6" t="str">
+        <x:v>开关</x:v>
+      </x:c>
+      <x:c r="E10" s="6" t="str">
+        <x:v>0 / 1</x:v>
+      </x:c>
+      <x:c r="F10" s="10" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G10" s="8" t="str">
+        <x:v>玄同授予本关对应随从的基础形态。0 关闭，1 开启；不撤回已经获得的随从。</x:v>
+      </x:c>
+      <x:c r="H10" s="6" t="str">
+        <x:v>reward:s07</x:v>
+      </x:c>
+      <x:c r="I10" s="6" t="str">
+        <x:v>fc_grants_base_pet</x:v>
+      </x:c>
+      <x:c r="J10" s="6" t="str">
+        <x:v>content/stages/s07/reward_definition.tres</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="46" customHeight="1">
+      <x:c r="A11" s="6" t="str">
+        <x:v>翼火蛇 · 至臻进阶</x:v>
+      </x:c>
+      <x:c r="B11" s="9" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C11" s="10" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D11" s="6" t="str">
+        <x:v>开关</x:v>
+      </x:c>
+      <x:c r="E11" s="6" t="str">
+        <x:v>0 / 1</x:v>
+      </x:c>
+      <x:c r="F11" s="10" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G11" s="8" t="str">
+        <x:v>至臻授予本关对应随从的进阶形态，并保证已收服。0 关闭，1 开启。</x:v>
+      </x:c>
+      <x:c r="H11" s="6" t="str">
+        <x:v>reward:s07</x:v>
+      </x:c>
+      <x:c r="I11" s="6" t="str">
+        <x:v>ap_grants_advanced_pet</x:v>
+      </x:c>
+      <x:c r="J11" s="6" t="str">
+        <x:v>content/stages/s07/reward_definition.tres</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="46" customHeight="1">
+      <x:c r="A12" s="6" t="str">
+        <x:v>鬼金羊 · 下一关</x:v>
+      </x:c>
+      <x:c r="B12" s="50"/>
+      <x:c r="C12" s="47" t="str"/>
+      <x:c r="D12" s="6" t="str">
+        <x:v>关卡 ID</x:v>
+      </x:c>
+      <x:c r="E12" s="6" t="str">
+        <x:v>已登记关卡 ID / 留空</x:v>
+      </x:c>
+      <x:c r="F12" s="10" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G12" s="8" t="str">
+        <x:v>通关后解锁并提供下一关入口。填写关卡稳定 ID；留空表示末关。仅正式关卡使用。</x:v>
+      </x:c>
+      <x:c r="H12" s="6" t="str">
+        <x:v>reward:s08</x:v>
+      </x:c>
+      <x:c r="I12" s="6" t="str">
+        <x:v>next_stage_id</x:v>
+      </x:c>
+      <x:c r="J12" s="6" t="str">
+        <x:v>content/stages/s08/reward_definition.tres</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="46" customHeight="1">
+      <x:c r="A13" s="6" t="str">
+        <x:v>鬼金羊 · 玄同收服</x:v>
+      </x:c>
+      <x:c r="B13" s="9" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C13" s="10" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D13" s="6" t="str">
+        <x:v>开关</x:v>
+      </x:c>
+      <x:c r="E13" s="6" t="str">
+        <x:v>0 / 1</x:v>
+      </x:c>
+      <x:c r="F13" s="10" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G13" s="8" t="str">
+        <x:v>玄同授予本关对应随从的基础形态。0 关闭，1 开启；不撤回已经获得的随从。</x:v>
+      </x:c>
+      <x:c r="H13" s="6" t="str">
+        <x:v>reward:s08</x:v>
+      </x:c>
+      <x:c r="I13" s="6" t="str">
+        <x:v>fc_grants_base_pet</x:v>
+      </x:c>
+      <x:c r="J13" s="6" t="str">
+        <x:v>content/stages/s08/reward_definition.tres</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="46" customHeight="1">
+      <x:c r="A14" s="6" t="str">
+        <x:v>鬼金羊 · 至臻进阶</x:v>
+      </x:c>
+      <x:c r="B14" s="9" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C14" s="10" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D14" s="6" t="str">
+        <x:v>开关</x:v>
+      </x:c>
+      <x:c r="E14" s="6" t="str">
+        <x:v>0 / 1</x:v>
+      </x:c>
+      <x:c r="F14" s="10" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G14" s="8" t="str">
+        <x:v>至臻授予本关对应随从的进阶形态，并保证已收服。0 关闭，1 开启。</x:v>
+      </x:c>
+      <x:c r="H14" s="6" t="str">
+        <x:v>reward:s08</x:v>
+      </x:c>
+      <x:c r="I14" s="6" t="str">
+        <x:v>ap_grants_advanced_pet</x:v>
+      </x:c>
+      <x:c r="J14" s="6" t="str">
+        <x:v>content/stages/s08/reward_definition.tres</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:dataValidations count="6">
+    <x:dataValidation type="whole" operator="between" sqref="B7">
+      <x:formula1>0</x:formula1>
+      <x:formula2>1</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="whole" operator="between" sqref="B8">
+      <x:formula1>0</x:formula1>
+      <x:formula2>1</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="whole" operator="between" sqref="B10">
+      <x:formula1>0</x:formula1>
+      <x:formula2>1</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="whole" operator="between" sqref="B11">
+      <x:formula1>0</x:formula1>
+      <x:formula2>1</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="whole" operator="between" sqref="B13">
+      <x:formula1>0</x:formula1>
+      <x:formula2>1</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="whole" operator="between" sqref="B14">
+      <x:formula1>0</x:formula1>
+      <x:formula2>1</x:formula2>
+    </x:dataValidation>
+  </x:dataValidations>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="13" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="13" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="15" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="30" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="72" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="32" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="40" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="58" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="2">
+      <x:c r="A2" s="2" t="str">
+        <x:v>开屏引导</x:v>
+      </x:c>
+      <x:c r="B2" s="1"/>
+      <x:c r="C2" s="1"/>
+      <x:c r="D2" s="1"/>
+      <x:c r="E2" s="1"/>
+      <x:c r="F2" s="1"/>
+      <x:c r="G2" s="1"/>
+      <x:c r="H2" s="1"/>
+      <x:c r="I2" s="1"/>
+      <x:c r="J2" s="1"/>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="1" t="str">
+        <x:v>修改黄色当前值，下次启动正式游戏生效；操作说明由玩家确认后继续。</x:v>
+      </x:c>
+      <x:c r="B3" s="1"/>
+      <x:c r="C3" s="1"/>
+      <x:c r="D3" s="1"/>
+      <x:c r="E3" s="1"/>
+      <x:c r="F3" s="1"/>
+      <x:c r="G3" s="1"/>
+      <x:c r="H3" s="1"/>
+      <x:c r="I3" s="1"/>
+      <x:c r="J3" s="1"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="1"/>
+      <x:c r="B4" s="1"/>
+      <x:c r="C4" s="1"/>
+      <x:c r="D4" s="1"/>
+      <x:c r="E4" s="1"/>
+      <x:c r="F4" s="1"/>
+      <x:c r="G4" s="1"/>
+      <x:c r="H4" s="1"/>
+      <x:c r="I4" s="1"/>
+      <x:c r="J4" s="1"/>
+    </x:row>
+    <x:row r="5" ht="30" customHeight="1">
+      <x:c r="A5" s="91" t="str">
+        <x:v>参数</x:v>
+      </x:c>
+      <x:c r="B5" s="91" t="str">
+        <x:v>当前值</x:v>
+      </x:c>
+      <x:c r="C5" s="91" t="str">
+        <x:v>原型默认</x:v>
+      </x:c>
+      <x:c r="D5" s="91" t="str">
+        <x:v>单位</x:v>
+      </x:c>
+      <x:c r="E5" s="91" t="str">
+        <x:v>建议试调区间</x:v>
+      </x:c>
+      <x:c r="F5" s="91" t="str">
+        <x:v>每次建议改动</x:v>
+      </x:c>
+      <x:c r="G5" s="91" t="str">
+        <x:v>作用与注意事项</x:v>
+      </x:c>
+      <x:c r="H5" s="91" t="str">
+        <x:v>配置对象</x:v>
+      </x:c>
+      <x:c r="I5" s="91" t="str">
+        <x:v>字段名</x:v>
+      </x:c>
+      <x:c r="J5" s="91" t="str">
+        <x:v>来源（Game 内）</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="46" customHeight="1">
+      <x:c r="A6" s="6" t="str">
+        <x:v>页面淡入</x:v>
+      </x:c>
+      <x:c r="B6" s="21" t="n">
+        <x:v>0.6</x:v>
+      </x:c>
+      <x:c r="C6" s="20" t="n">
+        <x:v>0.6</x:v>
+      </x:c>
+      <x:c r="D6" s="6" t="str">
+        <x:v>秒</x:v>
+      </x:c>
+      <x:c r="E6" s="6" t="str">
+        <x:v>0.3～1</x:v>
+      </x:c>
+      <x:c r="F6" s="20" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="G6" s="8" t="str">
+        <x:v>MEMO、耳机提示、操作说明的淡入时长。</x:v>
+      </x:c>
+      <x:c r="H6" s="6" t="str">
+        <x:v>ui_guides</x:v>
+      </x:c>
+      <x:c r="I6" s="6" t="str">
+        <x:v>fade_in_sec</x:v>
+      </x:c>
+      <x:c r="J6" s="6" t="str">
+        <x:v>src/app/ui/boot_splash.gd</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="46" customHeight="1">
+      <x:c r="A7" s="6" t="str">
+        <x:v>MEMO 停留</x:v>
+      </x:c>
+      <x:c r="B7" s="21" t="n">
+        <x:v>1.2</x:v>
+      </x:c>
+      <x:c r="C7" s="20" t="n">
+        <x:v>1.2</x:v>
+      </x:c>
+      <x:c r="D7" s="6" t="str">
+        <x:v>秒</x:v>
+      </x:c>
+      <x:c r="E7" s="6" t="str">
+        <x:v>1～3</x:v>
+      </x:c>
+      <x:c r="F7" s="20" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="G7" s="8" t="str">
+        <x:v>工作室图样完整显示后的停留时长，之后显示耳机提示。</x:v>
+      </x:c>
+      <x:c r="H7" s="6" t="str">
+        <x:v>ui_guides</x:v>
+      </x:c>
+      <x:c r="I7" s="6" t="str">
+        <x:v>hold_sec</x:v>
+      </x:c>
+      <x:c r="J7" s="6" t="str">
+        <x:v>src/app/ui/boot_splash.gd</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="46" customHeight="1">
+      <x:c r="A8" s="6" t="str">
+        <x:v>页面淡出</x:v>
+      </x:c>
+      <x:c r="B8" s="21" t="n">
+        <x:v>0.6</x:v>
+      </x:c>
+      <x:c r="C8" s="20" t="n">
+        <x:v>0.6</x:v>
+      </x:c>
+      <x:c r="D8" s="6" t="str">
+        <x:v>秒</x:v>
+      </x:c>
+      <x:c r="E8" s="6" t="str">
+        <x:v>0.3～1</x:v>
+      </x:c>
+      <x:c r="F8" s="20" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="G8" s="8" t="str">
+        <x:v>MEMO、耳机提示、操作说明的淡出时长；最后另有固定 0.3 秒黑场过渡。</x:v>
+      </x:c>
+      <x:c r="H8" s="6" t="str">
+        <x:v>ui_guides</x:v>
+      </x:c>
+      <x:c r="I8" s="6" t="str">
+        <x:v>fade_out_sec</x:v>
+      </x:c>
+      <x:c r="J8" s="6" t="str">
+        <x:v>src/app/ui/boot_splash.gd</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="46" customHeight="1">
+      <x:c r="A9" s="6" t="str">
+        <x:v>耳机提示停留</x:v>
+      </x:c>
+      <x:c r="B9" s="21" t="n">
+        <x:v>2.4</x:v>
+      </x:c>
+      <x:c r="C9" s="20" t="n">
+        <x:v>2.4</x:v>
+      </x:c>
+      <x:c r="D9" s="6" t="str">
+        <x:v>秒</x:v>
+      </x:c>
+      <x:c r="E9" s="6" t="str">
+        <x:v>2～4</x:v>
+      </x:c>
+      <x:c r="F9" s="20" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="G9" s="8" t="str">
+        <x:v>耳机图样和提示语完整显示后的停留时长；操作说明没有自动关闭倒计时。</x:v>
+      </x:c>
+      <x:c r="H9" s="6" t="str">
+        <x:v>ui_guides</x:v>
+      </x:c>
+      <x:c r="I9" s="6" t="str">
+        <x:v>headphones_hold_sec</x:v>
+      </x:c>
+      <x:c r="J9" s="6" t="str">
+        <x:v>src/app/ui/boot_splash.gd</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:dataValidations count="4">
+    <x:dataValidation type="decimal" operator="between" sqref="B6">
+      <x:formula1>0.1</x:formula1>
+      <x:formula2>2</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="decimal" operator="between" sqref="B7">
+      <x:formula1>0.1</x:formula1>
+      <x:formula2>8</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="decimal" operator="between" sqref="B8">
+      <x:formula1>0.1</x:formula1>
+      <x:formula2>2</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="decimal" operator="between" sqref="B9">
+      <x:formula1>0.1</x:formula1>
+      <x:formula2>10</x:formula2>
+    </x:dataValidation>
+  </x:dataValidations>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="13" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="13" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="15" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="30" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="72" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="32" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="40" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="58" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="2">
+      <x:c r="A2" s="2" t="str">
+        <x:v>判定表现</x:v>
+      </x:c>
+      <x:c r="B2" s="1"/>
+      <x:c r="C2" s="1"/>
+      <x:c r="D2" s="1"/>
+      <x:c r="E2" s="1"/>
+      <x:c r="F2" s="1"/>
+      <x:c r="G2" s="1"/>
+      <x:c r="H2" s="1"/>
+      <x:c r="I2" s="1"/>
+      <x:c r="J2" s="1"/>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="1" t="str">
+        <x:v>修改黄色“当前值”，保存后重新装载关卡。比例用小数，开关用 0 / 1。</x:v>
+      </x:c>
+      <x:c r="B3" s="1"/>
+      <x:c r="C3" s="1"/>
+      <x:c r="D3" s="1"/>
+      <x:c r="E3" s="1"/>
+      <x:c r="F3" s="1"/>
+      <x:c r="G3" s="1"/>
+      <x:c r="H3" s="1"/>
+      <x:c r="I3" s="1"/>
+      <x:c r="J3" s="1"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="1"/>
+      <x:c r="B4" s="1"/>
+      <x:c r="C4" s="1"/>
+      <x:c r="D4" s="1"/>
+      <x:c r="E4" s="1"/>
+      <x:c r="F4" s="1"/>
+      <x:c r="G4" s="1"/>
+      <x:c r="H4" s="1"/>
+      <x:c r="I4" s="1"/>
+      <x:c r="J4" s="1"/>
+    </x:row>
+    <x:row r="5" ht="30" customHeight="1">
+      <x:c r="A5" s="97" t="str">
+        <x:v>参数</x:v>
+      </x:c>
+      <x:c r="B5" s="97" t="str">
+        <x:v>当前值</x:v>
+      </x:c>
+      <x:c r="C5" s="97" t="str">
+        <x:v>原型默认</x:v>
+      </x:c>
+      <x:c r="D5" s="97" t="str">
+        <x:v>单位</x:v>
+      </x:c>
+      <x:c r="E5" s="97" t="str">
+        <x:v>建议试调区间</x:v>
+      </x:c>
+      <x:c r="F5" s="97" t="str">
+        <x:v>每次建议改动</x:v>
+      </x:c>
+      <x:c r="G5" s="97" t="str">
+        <x:v>作用与注意事项</x:v>
+      </x:c>
+      <x:c r="H5" s="97" t="str">
+        <x:v>配置对象</x:v>
+      </x:c>
+      <x:c r="I5" s="97" t="str">
+        <x:v>字段名</x:v>
+      </x:c>
+      <x:c r="J5" s="97" t="str">
+        <x:v>来源（Game 内）</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="46" customHeight="1">
+      <x:c r="A6" s="6" t="str">
+        <x:v>判定字形基准高度</x:v>
+      </x:c>
+      <x:c r="B6" s="99" t="n">
+        <x:v>640</x:v>
+      </x:c>
+      <x:c r="C6" s="20" t="n">
+        <x:v>640</x:v>
+      </x:c>
+      <x:c r="D6" s="6" t="str">
+        <x:v>设计 px</x:v>
+      </x:c>
+      <x:c r="E6" s="6" t="str">
+        <x:v>512～800</x:v>
+      </x:c>
+      <x:c r="F6" s="10" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G6" s="8" t="str">
+        <x:v>以实体笔画包围盒等高归一；乘现有 scale=0.25，默认实际高度 160 px。</x:v>
+      </x:c>
+      <x:c r="H6" s="6" t="str">
+        <x:v>judgment</x:v>
+      </x:c>
+      <x:c r="I6" s="6" t="str">
+        <x:v>glyph_height</x:v>
+      </x:c>
+      <x:c r="J6" s="6" t="str">
+        <x:v>src/content/resources/judgment_texture_set.gd</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="46" customHeight="1">
+      <x:c r="A7" s="6" t="str">
+        <x:v>判定不透明度</x:v>
+      </x:c>
+      <x:c r="B7" s="100" t="n">
+        <x:v>0.7</x:v>
+      </x:c>
+      <x:c r="C7" s="12" t="n">
+        <x:v>0.7</x:v>
+      </x:c>
+      <x:c r="D7" s="6" t="str">
+        <x:v>比例</x:v>
+      </x:c>
+      <x:c r="E7" s="6" t="str">
+        <x:v>0.5～0.8</x:v>
+      </x:c>
+      <x:c r="F7" s="12" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="G7" s="8" t="str">
+        <x:v>字形和对应光效的最终透明度上限，随原有判定动画淡出。</x:v>
+      </x:c>
+      <x:c r="H7" s="6" t="str">
+        <x:v>judgment</x:v>
+      </x:c>
+      <x:c r="I7" s="6" t="str">
+        <x:v>opacity</x:v>
+      </x:c>
+      <x:c r="J7" s="6" t="str">
+        <x:v>src/content/resources/judgment_texture_set.gd</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="46" customHeight="1">
+      <x:c r="A8" s="6" t="str">
+        <x:v>判定柔光半径</x:v>
+      </x:c>
+      <x:c r="B8" s="99" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C8" s="20" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D8" s="6" t="str">
+        <x:v>设计 px</x:v>
+      </x:c>
+      <x:c r="E8" s="6" t="str">
+        <x:v>8～18</x:v>
+      </x:c>
+      <x:c r="F8" s="10" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G8" s="8" t="str">
+        <x:v>实体笔触外侧的柔光范围；边距自动预留，不裁切。</x:v>
+      </x:c>
+      <x:c r="H8" s="6" t="str">
+        <x:v>judgment</x:v>
+      </x:c>
+      <x:c r="I8" s="6" t="str">
+        <x:v>glow_radius_px</x:v>
+      </x:c>
+      <x:c r="J8" s="6" t="str">
+        <x:v>src/content/resources/judgment_texture_set.gd</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="46" customHeight="1">
+      <x:c r="A9" s="6" t="str">
+        <x:v>判定柔光强度</x:v>
+      </x:c>
+      <x:c r="B9" s="99" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="C9" s="20" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="D9" s="6" t="str">
+        <x:v>倍率</x:v>
+      </x:c>
+      <x:c r="E9" s="6" t="str">
+        <x:v>1～2</x:v>
+      </x:c>
+      <x:c r="F9" s="20" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="G9" s="8" t="str">
+        <x:v>同色柔光强度，0 关闭；不会把实体透明度叠加至 70% 以上。</x:v>
+      </x:c>
+      <x:c r="H9" s="6" t="str">
+        <x:v>judgment</x:v>
+      </x:c>
+      <x:c r="I9" s="6" t="str">
+        <x:v>glow_strength</x:v>
+      </x:c>
+      <x:c r="J9" s="6" t="str">
+        <x:v>src/content/resources/judgment_texture_set.gd</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="46" customHeight="1">
+      <x:c r="A10" s="6" t="str">
+        <x:v>臻 · 橙黄色</x:v>
+      </x:c>
+      <x:c r="B10" s="101" t="str">
+        <x:v>#ffba48</x:v>
+      </x:c>
+      <x:c r="C10" s="47" t="str">
+        <x:v>#ffba48</x:v>
+      </x:c>
+      <x:c r="D10" s="6" t="str">
+        <x:v>颜色</x:v>
+      </x:c>
+      <x:c r="E10" s="6" t="str">
+        <x:v>#RRGGBB</x:v>
+      </x:c>
+      <x:c r="F10" s="10" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G10" s="8" t="str">
+        <x:v>实体笔画及柔晕共用的颜色；保留原图笔画形状，去除原有异色低透明光晕。</x:v>
+      </x:c>
+      <x:c r="H10" s="6" t="str">
+        <x:v>judgment</x:v>
+      </x:c>
+      <x:c r="I10" s="6" t="str">
+        <x:v>perfect_color</x:v>
+      </x:c>
+      <x:c r="J10" s="6" t="str">
+        <x:v>src/content/resources/judgment_texture_set.gd</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="46" customHeight="1">
+      <x:c r="A11" s="6" t="str">
+        <x:v>良 · 绿色</x:v>
+      </x:c>
+      <x:c r="B11" s="101" t="str">
+        <x:v>#77d68d</x:v>
+      </x:c>
+      <x:c r="C11" s="47" t="str">
+        <x:v>#77d68d</x:v>
+      </x:c>
+      <x:c r="D11" s="6" t="str">
+        <x:v>颜色</x:v>
+      </x:c>
+      <x:c r="E11" s="6" t="str">
+        <x:v>#RRGGBB</x:v>
+      </x:c>
+      <x:c r="F11" s="10" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G11" s="8" t="str">
+        <x:v>实体笔画及柔晕共用的颜色；保留原图笔画形状，去除原有异色低透明光晕。</x:v>
+      </x:c>
+      <x:c r="H11" s="6" t="str">
+        <x:v>judgment</x:v>
+      </x:c>
+      <x:c r="I11" s="6" t="str">
+        <x:v>good_color</x:v>
+      </x:c>
+      <x:c r="J11" s="6" t="str">
+        <x:v>src/content/resources/judgment_texture_set.gd</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="46" customHeight="1">
+      <x:c r="A12" s="6" t="str">
+        <x:v>过 · 灰蓝色</x:v>
+      </x:c>
+      <x:c r="B12" s="101" t="str">
+        <x:v>#8fa7bd</x:v>
+      </x:c>
+      <x:c r="C12" s="47" t="str">
+        <x:v>#8fa7bd</x:v>
+      </x:c>
+      <x:c r="D12" s="6" t="str">
+        <x:v>颜色</x:v>
+      </x:c>
+      <x:c r="E12" s="6" t="str">
+        <x:v>#RRGGBB</x:v>
+      </x:c>
+      <x:c r="F12" s="10" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G12" s="8" t="str">
+        <x:v>实体笔画及柔晕共用的颜色；保留原图笔画形状，去除原有异色低透明光晕。</x:v>
+      </x:c>
+      <x:c r="H12" s="6" t="str">
+        <x:v>judgment</x:v>
+      </x:c>
+      <x:c r="I12" s="6" t="str">
+        <x:v>pass_color</x:v>
+      </x:c>
+      <x:c r="J12" s="6" t="str">
+        <x:v>src/content/resources/judgment_texture_set.gd</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="46" customHeight="1">
+      <x:c r="A13" s="6" t="str">
+        <x:v>失 · 灰色</x:v>
+      </x:c>
+      <x:c r="B13" s="101" t="str">
+        <x:v>#a5a5a5</x:v>
+      </x:c>
+      <x:c r="C13" s="47" t="str">
+        <x:v>#a5a5a5</x:v>
+      </x:c>
+      <x:c r="D13" s="6" t="str">
+        <x:v>颜色</x:v>
+      </x:c>
+      <x:c r="E13" s="6" t="str">
+        <x:v>#RRGGBB</x:v>
+      </x:c>
+      <x:c r="F13" s="10" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G13" s="8" t="str">
+        <x:v>实体笔画及柔晕共用的颜色；保留原图笔画形状，去除原有异色低透明光晕。</x:v>
+      </x:c>
+      <x:c r="H13" s="6" t="str">
+        <x:v>judgment</x:v>
+      </x:c>
+      <x:c r="I13" s="6" t="str">
+        <x:v>miss_color</x:v>
+      </x:c>
+      <x:c r="J13" s="6" t="str">
+        <x:v>src/content/resources/judgment_texture_set.gd</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:dataValidations count="4">
+    <x:dataValidation type="decimal" operator="between" sqref="B6">
+      <x:formula1>128</x:formula1>
+      <x:formula2>1200</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="decimal" operator="between" sqref="B7">
+      <x:formula1>0</x:formula1>
+      <x:formula2>1</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="decimal" operator="between" sqref="B8">
+      <x:formula1>0</x:formula1>
+      <x:formula2>32</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="decimal" operator="between" sqref="B9">
+      <x:formula1>0</x:formula1>
+      <x:formula2>3</x:formula2>
+    </x:dataValidation>
+  </x:dataValidations>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
@@ -2945,8 +4189,40 @@
         <x:v>src/content/resources/gameplay_rule_set.gd</x:v>
       </x:c>
     </x:row>
+    <x:row r="8" ht="46" customHeight="1">
+      <x:c r="A8" s="6" t="str">
+        <x:v>Ghost 额外预告</x:v>
+      </x:c>
+      <x:c r="B8" s="21" t="n">
+        <x:v>0.45</x:v>
+      </x:c>
+      <x:c r="C8" s="20" t="n">
+        <x:v>0.45</x:v>
+      </x:c>
+      <x:c r="D8" s="6" t="str">
+        <x:v>s</x:v>
+      </x:c>
+      <x:c r="E8" s="6" t="str">
+        <x:v>0.2～0.8</x:v>
+      </x:c>
+      <x:c r="F8" s="20" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="G8" s="8" t="str">
+        <x:v>在普通接近时间前额外显示闭眼 Ghost；同步提前固定预测位置的取样边界，不改变结算时刻、调频评分或伤害。</x:v>
+      </x:c>
+      <x:c r="H8" s="6" t="str">
+        <x:v>rules</x:v>
+      </x:c>
+      <x:c r="I8" s="6" t="str">
+        <x:v>ghost_preview_extra_sec</x:v>
+      </x:c>
+      <x:c r="J8" s="6" t="str">
+        <x:v>src/content/resources/gameplay_rule_set.gd</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:dataValidations count="2">
+  <x:dataValidations count="3">
     <x:dataValidation type="decimal" operator="between" sqref="B6">
       <x:formula1>0.1</x:formula1>
       <x:formula2>10</x:formula2>
@@ -2954,6 +4230,10 @@
     <x:dataValidation type="decimal" operator="between" sqref="B7">
       <x:formula1>10</x:formula1>
       <x:formula2>4000</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="decimal" operator="between" sqref="B8">
+      <x:formula1>0</x:formula1>
+      <x:formula2>2</x:formula2>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3050,7 +4330,7 @@
     </x:row>
     <x:row r="6" ht="36" customHeight="1">
       <x:c r="A6" s="6" t="str">
-        <x:v>蝠漆漆·基础 得分加成</x:v>
+        <x:v>女土蝠·基础 得分加成</x:v>
       </x:c>
       <x:c r="B6" s="11" t="n">
         <x:v>0.02</x:v>
@@ -3082,7 +4362,7 @@
     </x:row>
     <x:row r="7" ht="36" customHeight="1">
       <x:c r="A7" s="6" t="str">
-        <x:v>蝠漆漆·进阶 得分加成</x:v>
+        <x:v>女土蝠·进阶 得分加成</x:v>
       </x:c>
       <x:c r="B7" s="11" t="n">
         <x:v>0.03</x:v>
@@ -3114,7 +4394,7 @@
     </x:row>
     <x:row r="8" ht="36" customHeight="1">
       <x:c r="A8" s="6" t="str">
-        <x:v>羊头仔·基础 减伤</x:v>
+        <x:v>鬼金羊·基础 减伤</x:v>
       </x:c>
       <x:c r="B8" s="11" t="n">
         <x:v>0.1</x:v>
@@ -3146,7 +4426,7 @@
     </x:row>
     <x:row r="9" ht="36" customHeight="1">
       <x:c r="A9" s="6" t="str">
-        <x:v>羊头仔·进阶 减伤</x:v>
+        <x:v>鬼金羊·进阶 减伤</x:v>
       </x:c>
       <x:c r="B9" s="11" t="n">
         <x:v>0.2</x:v>
@@ -3178,7 +4458,7 @@
     </x:row>
     <x:row r="10" ht="36" customHeight="1">
       <x:c r="A10" s="6" t="str">
-        <x:v>苹果蛇·基础 头部宽限</x:v>
+        <x:v>翼火蛇·基础 头部宽限</x:v>
       </x:c>
       <x:c r="B10" s="9" t="n">
         <x:v>10</x:v>
@@ -3210,7 +4490,7 @@
     </x:row>
     <x:row r="11" ht="36" customHeight="1">
       <x:c r="A11" s="6" t="str">
-        <x:v>苹果蛇·进阶 头部宽限</x:v>
+        <x:v>翼火蛇·进阶 头部宽限</x:v>
       </x:c>
       <x:c r="B11" s="9" t="n">
         <x:v>10</x:v>
@@ -3242,7 +4522,7 @@
     </x:row>
     <x:row r="12" ht="36" customHeight="1">
       <x:c r="A12" s="6" t="str">
-        <x:v>苹果蛇·基础 断持宽限</x:v>
+        <x:v>翼火蛇·基础 断持宽限</x:v>
       </x:c>
       <x:c r="B12" s="9" t="n">
         <x:v>20</x:v>
@@ -3274,7 +4554,7 @@
     </x:row>
     <x:row r="13" ht="36" customHeight="1">
       <x:c r="A13" s="6" t="str">
-        <x:v>苹果蛇·进阶 断持宽限</x:v>
+        <x:v>翼火蛇·进阶 断持宽限</x:v>
       </x:c>
       <x:c r="B13" s="9" t="n">
         <x:v>20</x:v>
@@ -3306,7 +4586,7 @@
     </x:row>
     <x:row r="14" ht="36" customHeight="1">
       <x:c r="A14" s="6" t="str">
-        <x:v>苹果蛇·基础 判定提升</x:v>
+        <x:v>翼火蛇·基础 判定提升</x:v>
       </x:c>
       <x:c r="B14" s="9" t="n">
         <x:v>0</x:v>
@@ -3338,7 +4618,7 @@
     </x:row>
     <x:row r="15" ht="36" customHeight="1">
       <x:c r="A15" s="6" t="str">
-        <x:v>苹果蛇·进阶 判定提升</x:v>
+        <x:v>翼火蛇·进阶 判定提升</x:v>
       </x:c>
       <x:c r="B15" s="9" t="n">
         <x:v>1</x:v>
@@ -3539,7 +4819,7 @@
       <x:c r="A7" s="6" t="str">
         <x:v>已停用：缓流周期</x:v>
       </x:c>
-      <x:c r="B7" s="66" t="n">
+      <x:c r="B7" s="87" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="C7" s="20" t="n">
@@ -3567,7 +4847,7 @@
       <x:c r="A8" s="6" t="str">
         <x:v>已停用：水带起伏</x:v>
       </x:c>
-      <x:c r="B8" s="66" t="n">
+      <x:c r="B8" s="87" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C8" s="20" t="n">
@@ -3595,7 +4875,7 @@
       <x:c r="A9" s="6" t="str">
         <x:v>已停用：大浪回卷</x:v>
       </x:c>
-      <x:c r="B9" s="66" t="n">
+      <x:c r="B9" s="87" t="n">
         <x:v>12</x:v>
       </x:c>
       <x:c r="C9" s="20" t="n">
@@ -3623,7 +4903,7 @@
       <x:c r="A10" s="6" t="str">
         <x:v>已停用：节拍回应</x:v>
       </x:c>
-      <x:c r="B10" s="67" t="n">
+      <x:c r="B10" s="88" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C10" s="10" t="n">
@@ -3651,7 +4931,7 @@
       <x:c r="A11" s="6" t="str">
         <x:v>已停用：节拍舒张幅度</x:v>
       </x:c>
-      <x:c r="B11" s="66" t="n">
+      <x:c r="B11" s="87" t="n">
         <x:v>1.2</x:v>
       </x:c>
       <x:c r="C11" s="20" t="n">
@@ -3679,7 +4959,7 @@
       <x:c r="A12" s="6" t="str">
         <x:v>已停用：卷流接替间隔</x:v>
       </x:c>
-      <x:c r="B12" s="67" t="n">
+      <x:c r="B12" s="88" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C12" s="10" t="n">
@@ -3707,7 +4987,7 @@
       <x:c r="A13" s="6" t="str">
         <x:v>已停用：大浪高度</x:v>
       </x:c>
-      <x:c r="B13" s="66" t="n">
+      <x:c r="B13" s="87" t="n">
         <x:v>165</x:v>
       </x:c>
       <x:c r="C13" s="20" t="n">
@@ -3735,7 +5015,7 @@
       <x:c r="A14" s="6" t="str">
         <x:v>已停用：浪身推进</x:v>
       </x:c>
-      <x:c r="B14" s="66" t="n">
+      <x:c r="B14" s="87" t="n">
         <x:v>190</x:v>
       </x:c>
       <x:c r="C14" s="20" t="n">
@@ -3763,7 +5043,7 @@
       <x:c r="A15" s="6" t="str">
         <x:v>已停用：翻卷行程</x:v>
       </x:c>
-      <x:c r="B15" s="66" t="n">
+      <x:c r="B15" s="87" t="n">
         <x:v>90</x:v>
       </x:c>
       <x:c r="C15" s="20" t="n">
@@ -3791,7 +5071,7 @@
       <x:c r="A16" s="6" t="str">
         <x:v>已停用：拍落白沫强度</x:v>
       </x:c>
-      <x:c r="B16" s="68" t="n">
+      <x:c r="B16" s="89" t="n">
         <x:v>0.9</x:v>
       </x:c>
       <x:c r="C16" s="12" t="n">
@@ -3947,7 +5227,7 @@
       <x:c r="A21" s="6" t="str">
         <x:v>已停用：漩涡外半径</x:v>
       </x:c>
-      <x:c r="B21" s="66" t="n">
+      <x:c r="B21" s="87" t="n">
         <x:v>170</x:v>
       </x:c>
       <x:c r="C21" s="20" t="n">
@@ -4007,7 +5287,7 @@
       <x:c r="A23" s="6" t="str">
         <x:v>已停用：卷入角度</x:v>
       </x:c>
-      <x:c r="B23" s="66" t="n">
+      <x:c r="B23" s="87" t="n">
         <x:v>240</x:v>
       </x:c>
       <x:c r="C23" s="20" t="n">
@@ -4099,7 +5379,7 @@
       <x:c r="A26" s="6" t="str">
         <x:v>卷流速度</x:v>
       </x:c>
-      <x:c r="B26" s="70" t="n">
+      <x:c r="B26" s="21" t="n">
         <x:v>96</x:v>
       </x:c>
       <x:c r="C26" s="20" t="n">
@@ -4131,7 +5411,7 @@
       <x:c r="A27" s="6" t="str">
         <x:v>每拍推进</x:v>
       </x:c>
-      <x:c r="B27" s="70" t="n">
+      <x:c r="B27" s="21" t="n">
         <x:v>1.25</x:v>
       </x:c>
       <x:c r="C27" s="20" t="n">
@@ -4502,8 +5782,200 @@
         <x:v>src/content/resources/stage_visual_theme.gd</x:v>
       </x:c>
     </x:row>
+    <x:row r="11" ht="46" customHeight="1">
+      <x:c r="A11" s="6" t="str">
+        <x:v>人物横向偏移</x:v>
+      </x:c>
+      <x:c r="B11" s="21" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C11" s="20" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D11" s="6" t="str">
+        <x:v>设计 px</x:v>
+      </x:c>
+      <x:c r="E11" s="6" t="str">
+        <x:v>20～50</x:v>
+      </x:c>
+      <x:c r="F11" s="10" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G11" s="8" t="str">
+        <x:v>人物与附属编钟沿本侧局部 X 移动，死侧中心对称；不改变玩法波源。</x:v>
+      </x:c>
+      <x:c r="H11" s="6" t="str">
+        <x:v>actors</x:v>
+      </x:c>
+      <x:c r="I11" s="6" t="str">
+        <x:v>actor_shift_px</x:v>
+      </x:c>
+      <x:c r="J11" s="6" t="str">
+        <x:v>src/content/resources/stage_visual_theme.gd</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="46" customHeight="1">
+      <x:c r="A12" s="6" t="str">
+        <x:v>编钟向人物收近</x:v>
+      </x:c>
+      <x:c r="B12" s="21" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C12" s="20" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="D12" s="6" t="str">
+        <x:v>设计 px</x:v>
+      </x:c>
+      <x:c r="E12" s="6" t="str">
+        <x:v>12～40</x:v>
+      </x:c>
+      <x:c r="F12" s="10" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G12" s="8" t="str">
+        <x:v>相对场景原始人钟间距向内收近；正数缩短距离，不移动人物。</x:v>
+      </x:c>
+      <x:c r="H12" s="6" t="str">
+        <x:v>actors</x:v>
+      </x:c>
+      <x:c r="I12" s="6" t="str">
+        <x:v>bell_inset_px</x:v>
+      </x:c>
+      <x:c r="J12" s="6" t="str">
+        <x:v>src/content/resources/stage_visual_theme.gd</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="46" customHeight="1">
+      <x:c r="A13" s="6" t="str">
+        <x:v>宠物横向偏移</x:v>
+      </x:c>
+      <x:c r="B13" s="21" t="n">
+        <x:v>-60</x:v>
+      </x:c>
+      <x:c r="C13" s="20" t="n">
+        <x:v>-60</x:v>
+      </x:c>
+      <x:c r="D13" s="6" t="str">
+        <x:v>设计 px</x:v>
+      </x:c>
+      <x:c r="E13" s="6" t="str">
+        <x:v>-80～-40</x:v>
+      </x:c>
+      <x:c r="F13" s="10" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G13" s="8" t="str">
+        <x:v>叠加在随从锚点上，负数向本侧画面外移动；死侧中心对称。</x:v>
+      </x:c>
+      <x:c r="H13" s="6" t="str">
+        <x:v>actors</x:v>
+      </x:c>
+      <x:c r="I13" s="6" t="str">
+        <x:v>pet_shift_px</x:v>
+      </x:c>
+      <x:c r="J13" s="6" t="str">
+        <x:v>src/content/resources/stage_visual_theme.gd</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="46" customHeight="1">
+      <x:c r="A14" s="6" t="str">
+        <x:v>宠物大小倍率</x:v>
+      </x:c>
+      <x:c r="B14" s="21" t="n">
+        <x:v>0.85</x:v>
+      </x:c>
+      <x:c r="C14" s="20" t="n">
+        <x:v>0.85</x:v>
+      </x:c>
+      <x:c r="D14" s="6" t="str">
+        <x:v>倍</x:v>
+      </x:c>
+      <x:c r="E14" s="6" t="str">
+        <x:v>0.75～0.95</x:v>
+      </x:c>
+      <x:c r="F14" s="20" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="G14" s="8" t="str">
+        <x:v>乘以随从资源原有 world_scale；不改变技能、头像或菜单尺寸。</x:v>
+      </x:c>
+      <x:c r="H14" s="6" t="str">
+        <x:v>actors</x:v>
+      </x:c>
+      <x:c r="I14" s="6" t="str">
+        <x:v>pet_scale_multiplier</x:v>
+      </x:c>
+      <x:c r="J14" s="6" t="str">
+        <x:v>src/content/resources/stage_visual_theme.gd</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="46" customHeight="1">
+      <x:c r="A15" s="6" t="str">
+        <x:v>编钟浮动幅度</x:v>
+      </x:c>
+      <x:c r="B15" s="21" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C15" s="20" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D15" s="6" t="str">
+        <x:v>设计 px</x:v>
+      </x:c>
+      <x:c r="E15" s="6" t="str">
+        <x:v>2～6</x:v>
+      </x:c>
+      <x:c r="F15" s="10" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G15" s="8" t="str">
+        <x:v>相对静止位置的上下最大偏移；随歌曲时钟，暂停冻结。</x:v>
+      </x:c>
+      <x:c r="H15" s="6" t="str">
+        <x:v>actors</x:v>
+      </x:c>
+      <x:c r="I15" s="6" t="str">
+        <x:v>bell_float_height_px</x:v>
+      </x:c>
+      <x:c r="J15" s="6" t="str">
+        <x:v>src/content/resources/stage_visual_theme.gd</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="46" customHeight="1">
+      <x:c r="A16" s="6" t="str">
+        <x:v>编钟光效强度</x:v>
+      </x:c>
+      <x:c r="B16" s="21" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C16" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D16" s="6" t="str">
+        <x:v>倍</x:v>
+      </x:c>
+      <x:c r="E16" s="6" t="str">
+        <x:v>0.6～1.4</x:v>
+      </x:c>
+      <x:c r="F16" s="20" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="G16" s="8" t="str">
+        <x:v>统一缩放阵营柔光与挥槌接触时的提亮，保留原金属纹理。</x:v>
+      </x:c>
+      <x:c r="H16" s="6" t="str">
+        <x:v>actors</x:v>
+      </x:c>
+      <x:c r="I16" s="6" t="str">
+        <x:v>bell_glow_strength</x:v>
+      </x:c>
+      <x:c r="J16" s="6" t="str">
+        <x:v>src/content/resources/stage_visual_theme.gd</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:dataValidations count="3">
+  <x:dataValidations count="9">
     <x:dataValidation type="decimal" operator="between" sqref="B6">
       <x:formula1>0.8</x:formula1>
       <x:formula2>3.2</x:formula2>
@@ -4515,6 +5987,30 @@
     <x:dataValidation type="decimal" operator="between" sqref="B8">
       <x:formula1>0.01</x:formula1>
       <x:formula2>10</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="decimal" operator="between" sqref="B11">
+      <x:formula1>-100</x:formula1>
+      <x:formula2>100</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="decimal" operator="between" sqref="B12">
+      <x:formula1>-60</x:formula1>
+      <x:formula2>100</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="decimal" operator="between" sqref="B13">
+      <x:formula1>-100</x:formula1>
+      <x:formula2>100</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="decimal" operator="between" sqref="B14">
+      <x:formula1>0.5</x:formula1>
+      <x:formula2>1.5</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="decimal" operator="between" sqref="B15">
+      <x:formula1>0</x:formula1>
+      <x:formula2>12</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="decimal" operator="between" sqref="B16">
+      <x:formula1>0</x:formula1>
+      <x:formula2>2</x:formula2>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/outputs/planning/策划参数.xlsx
+++ b/outputs/planning/策划参数.xlsx
@@ -2,20 +2,20 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用与量级" sheetId="1" r:id="Rffc3a45d618d4cbb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01 判定与容错" sheetId="2" r:id="Re46629753cf844aa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02 魂火与惩罚" sheetId="3" r:id="Rfcfeca461b234a98"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03 调频" sheetId="4" r:id="Rc227d69b65594de4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04 计分" sheetId="5" r:id="R27e56c37caeb4c29"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05 读谱与声波" sheetId="6" r:id="Rd62456e3c7e94ef0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06 随从" sheetId="7" r:id="R4275c21e90114ba2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07 分界线表现" sheetId="8" r:id="R18e784fca0da409d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08 角色移动" sheetId="9" r:id="Rb26277c02d554bfa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09 BOSS 表现" sheetId="10" r:id="Re72c04aedc13426d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10 UI 火框" sheetId="11" r:id="Rda7a750d22b94e54"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11 关卡奖励" sheetId="12" r:id="R73895b002b544f11"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12 开屏引导" sheetId="13" r:id="R8c433707ea804329"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13 判定表现" sheetId="14" r:id="R27e3beafddf24540"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用与量级" sheetId="1" r:id="Rb91cb0f40ce44329"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01 判定与容错" sheetId="2" r:id="R8ae49809b2614d4c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02 魂火与惩罚" sheetId="3" r:id="Rf768328fad7d4757"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03 调频" sheetId="4" r:id="R6550f373968744d6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04 计分" sheetId="5" r:id="Rc67c0d5b314e4619"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05 读谱与声波" sheetId="6" r:id="Rc9896214e0024a5d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06 随从" sheetId="7" r:id="R1e00365efe5b457f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07 分界线表现" sheetId="8" r:id="Rbb91ec6640234c3d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08 角色移动" sheetId="9" r:id="R2ea8c69afcc24eed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09 BOSS 表现" sheetId="10" r:id="R009a784e4e6f4c82"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10 UI 火框" sheetId="11" r:id="R21e4dd6b2f434644"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11 关卡奖励" sheetId="12" r:id="R166e6dd4241a4756"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12 开屏引导" sheetId="13" r:id="R73cfa877d29a4c4c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13 判定表现" sheetId="14" r:id="R31ea16a183cd4702"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1050,7 +1050,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="1" t="str">
-        <x:v>修改黄色当前值，重新打开 BOSS 审看场景后生效。</x:v>
+        <x:v>修改黄色当前值，重新装载关卡或 BOSS 审看场景后生效；对象和绑定可覆盖战斗及发射默认值。</x:v>
       </x:c>
       <x:c r="B3" s="1"/>
       <x:c r="C3" s="1"/>
@@ -1206,7 +1206,7 @@
       <x:c r="A9" s="6" t="str">
         <x:v>BOSS 血量比例</x:v>
       </x:c>
-      <x:c r="B9" s="95" t="n">
+      <x:c r="B9" s="21" t="n">
         <x:v>0.8</x:v>
       </x:c>
       <x:c r="C9" s="20" t="n">
@@ -1238,7 +1238,7 @@
       <x:c r="A10" s="6" t="str">
         <x:v>BOSS 巡航速度</x:v>
       </x:c>
-      <x:c r="B10" s="95" t="n">
+      <x:c r="B10" s="21" t="n">
         <x:v>600</x:v>
       </x:c>
       <x:c r="C10" s="20" t="n">
@@ -1270,7 +1270,7 @@
       <x:c r="A11" s="6" t="str">
         <x:v>BOSS 散射半角</x:v>
       </x:c>
-      <x:c r="B11" s="95" t="n">
+      <x:c r="B11" s="21" t="n">
         <x:v>30</x:v>
       </x:c>
       <x:c r="C11" s="20" t="n">

--- a/outputs/planning/策划参数.xlsx
+++ b/outputs/planning/策划参数.xlsx
@@ -2,20 +2,20 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用与量级" sheetId="1" r:id="Rb91cb0f40ce44329"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01 判定与容错" sheetId="2" r:id="R8ae49809b2614d4c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02 魂火与惩罚" sheetId="3" r:id="Rf768328fad7d4757"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03 调频" sheetId="4" r:id="R6550f373968744d6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04 计分" sheetId="5" r:id="Rc67c0d5b314e4619"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05 读谱与声波" sheetId="6" r:id="Rc9896214e0024a5d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06 随从" sheetId="7" r:id="R1e00365efe5b457f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07 分界线表现" sheetId="8" r:id="Rbb91ec6640234c3d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08 角色移动" sheetId="9" r:id="R2ea8c69afcc24eed"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09 BOSS 表现" sheetId="10" r:id="R009a784e4e6f4c82"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10 UI 火框" sheetId="11" r:id="R21e4dd6b2f434644"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11 关卡奖励" sheetId="12" r:id="R166e6dd4241a4756"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12 开屏引导" sheetId="13" r:id="R73cfa877d29a4c4c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13 判定表现" sheetId="14" r:id="R31ea16a183cd4702"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用与量级" sheetId="1" r:id="Rc61775e9c8e74b76"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01 判定与容错" sheetId="2" r:id="R31bab163afcf4ffa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02 魂火与惩罚" sheetId="3" r:id="R281d94e89df94517"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03 调频" sheetId="4" r:id="Rb3b6e0cd412744c9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04 计分" sheetId="5" r:id="R11fe6c11f1cd437e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05 读谱与声波" sheetId="6" r:id="R1d25ac8996314135"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06 随从" sheetId="7" r:id="R0fe8665dc796473b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07 分界线表现" sheetId="8" r:id="R43522da3aedb45c1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08 角色移动" sheetId="9" r:id="Re5f807f85cd6424b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09 BOSS 表现" sheetId="10" r:id="R9099b535eaed4492"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10 UI 火框" sheetId="11" r:id="R04c3c9774a5f45dc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11 关卡奖励" sheetId="12" r:id="R74280eb1d50748eb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12 开屏引导" sheetId="13" r:id="R96cc331cb891416c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13 判定表现" sheetId="14" r:id="Ra1a6ba18ff8f440e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -58,7 +58,7 @@
       <x:name val="Microsoft YaHei"/>
     </x:font>
   </x:fonts>
-  <x:fills count="36">
+  <x:fills count="37">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -235,6 +235,11 @@
         <x:fgColor rgb="FFFFF0C2"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF0C2"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="1">
     <x:border/>
@@ -242,7 +247,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="102">
+  <x:cellXfs count="104">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -505,6 +510,12 @@
       <x:alignment vertical="center"/>
     </x:xf>
     <x:xf numFmtId="206" fontId="1" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="36" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="205" fontId="1" fillId="36" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
   </x:cellXfs>
@@ -873,7 +884,7 @@
       </x:c>
       <x:c r="B16" s="1" t="n">
         <x:f>IF('02 魂火与惩罚'!B7=0,"不扣血",ROUNDUP('02 魂火与惩罚'!B6/'02 魂火与惩罚'!B7,0))</x:f>
-        <x:v>5</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C16" s="1"/>
       <x:c r="D16" s="1"/>
@@ -925,7 +936,7 @@
       </x:c>
       <x:c r="B20" s="1" t="n">
         <x:f>ROUND('02 魂火与惩罚'!B7*(1-'06 随从'!B8),0)</x:f>
-        <x:v>18</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C20" s="1"/>
       <x:c r="D20" s="1"/>
@@ -987,7 +998,7 @@
       </x:c>
       <x:c r="B27" s="1" t="n">
         <x:f>'02 魂火与惩罚'!B10/'02 魂火与惩罚'!B11</x:f>
-        <x:v>8</x:v>
+        <x:v>6.4</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="30" customHeight="1">
@@ -996,7 +1007,7 @@
       </x:c>
       <x:c r="B28" s="1" t="n">
         <x:f>ROUND(2*B27,0)</x:f>
-        <x:v>16</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="30" customHeight="1">
@@ -1005,7 +1016,7 @@
       </x:c>
       <x:c r="B29" s="1" t="n">
         <x:f>IF('02 魂火与惩罚'!B12=0,"不扣血",ROUNDUP('02 魂火与惩罚'!B6/'02 魂火与惩罚'!B12,0))</x:f>
-        <x:v>10</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
@@ -2266,23 +2277,23 @@
       <x:c r="A6" s="6" t="str">
         <x:v>判定字形基准高度</x:v>
       </x:c>
-      <x:c r="B6" s="99" t="n">
-        <x:v>640</x:v>
+      <x:c r="B6" s="21" t="n">
+        <x:v>480</x:v>
       </x:c>
       <x:c r="C6" s="20" t="n">
-        <x:v>640</x:v>
+        <x:v>480</x:v>
       </x:c>
       <x:c r="D6" s="6" t="str">
         <x:v>设计 px</x:v>
       </x:c>
       <x:c r="E6" s="6" t="str">
-        <x:v>512～800</x:v>
+        <x:v>448～496</x:v>
       </x:c>
       <x:c r="F6" s="10" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G6" s="8" t="str">
-        <x:v>以实体笔画包围盒等高归一；乘现有 scale=0.25，默认实际高度 160 px。</x:v>
+        <x:v>实体笔画等高归一；乘现有 scale=0.25，默认实际高度 120 px，略小于 132 px 判定圈。</x:v>
       </x:c>
       <x:c r="H6" s="6" t="str">
         <x:v>judgment</x:v>
@@ -2298,7 +2309,7 @@
       <x:c r="A7" s="6" t="str">
         <x:v>判定不透明度</x:v>
       </x:c>
-      <x:c r="B7" s="100" t="n">
+      <x:c r="B7" s="11" t="n">
         <x:v>0.7</x:v>
       </x:c>
       <x:c r="C7" s="12" t="n">
@@ -2330,7 +2341,7 @@
       <x:c r="A8" s="6" t="str">
         <x:v>判定柔光半径</x:v>
       </x:c>
-      <x:c r="B8" s="99" t="n">
+      <x:c r="B8" s="21" t="n">
         <x:v>12</x:v>
       </x:c>
       <x:c r="C8" s="20" t="n">
@@ -2362,7 +2373,7 @@
       <x:c r="A9" s="6" t="str">
         <x:v>判定柔光强度</x:v>
       </x:c>
-      <x:c r="B9" s="99" t="n">
+      <x:c r="B9" s="21" t="n">
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="C9" s="20" t="n">
@@ -2394,7 +2405,7 @@
       <x:c r="A10" s="6" t="str">
         <x:v>臻 · 橙黄色</x:v>
       </x:c>
-      <x:c r="B10" s="101" t="str">
+      <x:c r="B10" s="50" t="str">
         <x:v>#ffba48</x:v>
       </x:c>
       <x:c r="C10" s="47" t="str">
@@ -2426,7 +2437,7 @@
       <x:c r="A11" s="6" t="str">
         <x:v>良 · 绿色</x:v>
       </x:c>
-      <x:c r="B11" s="101" t="str">
+      <x:c r="B11" s="50" t="str">
         <x:v>#77d68d</x:v>
       </x:c>
       <x:c r="C11" s="47" t="str">
@@ -2458,7 +2469,7 @@
       <x:c r="A12" s="6" t="str">
         <x:v>过 · 灰蓝色</x:v>
       </x:c>
-      <x:c r="B12" s="101" t="str">
+      <x:c r="B12" s="50" t="str">
         <x:v>#8fa7bd</x:v>
       </x:c>
       <x:c r="C12" s="47" t="str">
@@ -2490,7 +2501,7 @@
       <x:c r="A13" s="6" t="str">
         <x:v>失 · 灰色</x:v>
       </x:c>
-      <x:c r="B13" s="101" t="str">
+      <x:c r="B13" s="50" t="str">
         <x:v>#a5a5a5</x:v>
       </x:c>
       <x:c r="C13" s="47" t="str">
@@ -2518,8 +2529,40 @@
         <x:v>src/content/resources/judgment_texture_set.gd</x:v>
       </x:c>
     </x:row>
+    <x:row r="14" ht="46" customHeight="1">
+      <x:c r="A14" s="6" t="str">
+        <x:v>判定位置微偏移</x:v>
+      </x:c>
+      <x:c r="B14" s="103" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C14" s="20" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D14" s="6" t="str">
+        <x:v>设计 px</x:v>
+      </x:c>
+      <x:c r="E14" s="6" t="str">
+        <x:v>1～3</x:v>
+      </x:c>
+      <x:c r="F14" s="20" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="G14" s="8" t="str">
+        <x:v>每次在中心周围圆形范围内随机偏移，整段动画不再移动；0 关闭。同一判定重演位置一致。</x:v>
+      </x:c>
+      <x:c r="H14" s="6" t="str">
+        <x:v>judgment</x:v>
+      </x:c>
+      <x:c r="I14" s="6" t="str">
+        <x:v>position_jitter_px</x:v>
+      </x:c>
+      <x:c r="J14" s="6" t="str">
+        <x:v>src/content/resources/judgment_texture_set.gd</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:dataValidations count="4">
+  <x:dataValidations count="5">
     <x:dataValidation type="decimal" operator="between" sqref="B6">
       <x:formula1>128</x:formula1>
       <x:formula2>1200</x:formula2>
@@ -2535,6 +2578,10 @@
     <x:dataValidation type="decimal" operator="between" sqref="B9">
       <x:formula1>0</x:formula1>
       <x:formula2>3</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="decimal" operator="between" sqref="B14">
+      <x:formula1>0</x:formula1>
+      <x:formula2>8</x:formula2>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2941,10 +2988,10 @@
         <x:v>Tap 漏击伤害</x:v>
       </x:c>
       <x:c r="B7" s="9" t="n">
-        <x:v>20</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C7" s="10" t="n">
-        <x:v>20</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D7" s="6" t="str">
         <x:v>点</x:v>
@@ -3036,11 +3083,11 @@
       <x:c r="A10" s="6" t="str">
         <x:v>Hold 每段身体伤害</x:v>
       </x:c>
-      <x:c r="B10" s="9" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C10" s="10" t="n">
-        <x:v>2</x:v>
+      <x:c r="B10" s="21" t="n">
+        <x:v>1.6</x:v>
+      </x:c>
+      <x:c r="C10" s="20" t="n">
+        <x:v>1.6</x:v>
       </x:c>
       <x:c r="D10" s="6" t="str">
         <x:v>点/段</x:v>
@@ -3048,11 +3095,11 @@
       <x:c r="E10" s="6" t="str">
         <x:v>1～4</x:v>
       </x:c>
-      <x:c r="F10" s="10" t="n">
-        <x:v>1</x:v>
+      <x:c r="F10" s="20" t="n">
+        <x:v>0.1</x:v>
       </x:c>
       <x:c r="G10" s="8" t="str">
-        <x:v>未消耗身体抵达角色后按拍逐段扣血；无额外头部或整条失败伤害。</x:v>
+        <x:v>未消耗身体抵达角色后按拍逐段扣血；支持小数并按漏失拍长累计取整，无额外头部或整条失败伤害。</x:v>
       </x:c>
       <x:c r="H10" s="6" t="str">
         <x:v>rules</x:v>
@@ -3101,10 +3148,10 @@
         <x:v>Ghost 漏击伤害</x:v>
       </x:c>
       <x:c r="B12" s="9" t="n">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C12" s="10" t="n">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D12" s="6" t="str">
         <x:v>点/枚</x:v>
@@ -3178,7 +3225,7 @@
       <x:formula1>0</x:formula1>
       <x:formula2>1</x:formula2>
     </x:dataValidation>
-    <x:dataValidation type="whole" operator="between" sqref="B10">
+    <x:dataValidation type="decimal" operator="between" sqref="B10">
       <x:formula1>0</x:formula1>
       <x:formula2>1000</x:formula2>
     </x:dataValidation>

--- a/outputs/planning/策划参数.xlsx
+++ b/outputs/planning/策划参数.xlsx
@@ -2,20 +2,20 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用与量级" sheetId="1" r:id="Rc61775e9c8e74b76"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01 判定与容错" sheetId="2" r:id="R31bab163afcf4ffa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02 魂火与惩罚" sheetId="3" r:id="R281d94e89df94517"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03 调频" sheetId="4" r:id="Rb3b6e0cd412744c9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04 计分" sheetId="5" r:id="R11fe6c11f1cd437e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05 读谱与声波" sheetId="6" r:id="R1d25ac8996314135"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06 随从" sheetId="7" r:id="R0fe8665dc796473b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07 分界线表现" sheetId="8" r:id="R43522da3aedb45c1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08 角色移动" sheetId="9" r:id="Re5f807f85cd6424b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09 BOSS 表现" sheetId="10" r:id="R9099b535eaed4492"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10 UI 火框" sheetId="11" r:id="R04c3c9774a5f45dc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11 关卡奖励" sheetId="12" r:id="R74280eb1d50748eb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12 开屏引导" sheetId="13" r:id="R96cc331cb891416c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13 判定表现" sheetId="14" r:id="Ra1a6ba18ff8f440e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用与量级" sheetId="1" r:id="R59cbc99f785d411c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01 判定与容错" sheetId="2" r:id="R1a21058193124a23"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02 魂火与惩罚" sheetId="3" r:id="R7de6dbe5e6424c35"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03 调频" sheetId="4" r:id="Rcdfa93105a154074"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04 计分" sheetId="5" r:id="R0d5d2955ee204259"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05 读谱与声波" sheetId="6" r:id="R9a83d9b0b4a54f6a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06 随从" sheetId="7" r:id="R37fd2ca63ffe4ea9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07 分界线表现" sheetId="8" r:id="R5cc4e3a37fbc4452"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08 角色移动" sheetId="9" r:id="R7bfc092b2a44491f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09 BOSS 表现" sheetId="10" r:id="R1ce664e7efc44e36"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10 UI 火框" sheetId="11" r:id="R6fe492598d0349e1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11 关卡奖励" sheetId="12" r:id="Re27fa730d8504a74"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12 开屏引导" sheetId="13" r:id="R37771a89deb24655"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13 判定表现" sheetId="14" r:id="R89b01d2c5ca24186"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -58,7 +58,7 @@
       <x:name val="Microsoft YaHei"/>
     </x:font>
   </x:fonts>
-  <x:fills count="37">
+  <x:fills count="43">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -240,6 +240,36 @@
         <x:fgColor rgb="FFFFF0C2"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE7E8EA"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE7E8EA"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF0C2"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE7E8EA"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF0C2"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE7E8EA"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="1">
     <x:border/>
@@ -247,7 +277,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="104">
+  <x:cellXfs count="120">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -516,6 +546,54 @@
       <x:alignment vertical="center"/>
     </x:xf>
     <x:xf numFmtId="205" fontId="1" fillId="36" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="205" fontId="1" fillId="37" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="37" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="1" fillId="37" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="205" fontId="1" fillId="38" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="38" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="1" fillId="38" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="39" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="205" fontId="1" fillId="39" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="205" fontId="1" fillId="40" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="40" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="1" fillId="40" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="41" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="1" fillId="41" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="205" fontId="1" fillId="42" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="42" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="1" fillId="42" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
   </x:cellXfs>
@@ -884,7 +962,7 @@
       </x:c>
       <x:c r="B16" s="1" t="n">
         <x:f>IF('02 魂火与惩罚'!B7=0,"不扣血",ROUNDUP('02 魂火与惩罚'!B6/'02 魂火与惩罚'!B7,0))</x:f>
-        <x:v>7</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C16" s="1"/>
       <x:c r="D16" s="1"/>
@@ -936,7 +1014,7 @@
       </x:c>
       <x:c r="B20" s="1" t="n">
         <x:f>ROUND('02 魂火与惩罚'!B7*(1-'06 随从'!B8),0)</x:f>
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C20" s="1"/>
       <x:c r="D20" s="1"/>
@@ -998,7 +1076,7 @@
       </x:c>
       <x:c r="B27" s="1" t="n">
         <x:f>'02 魂火与惩罚'!B10/'02 魂火与惩罚'!B11</x:f>
-        <x:v>6.4</x:v>
+        <x:v>4.8</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="30" customHeight="1">
@@ -1007,7 +1085,7 @@
       </x:c>
       <x:c r="B28" s="1" t="n">
         <x:f>ROUND(2*B27,0)</x:f>
-        <x:v>13</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="30" customHeight="1">
@@ -1016,7 +1094,7 @@
       </x:c>
       <x:c r="B29" s="1" t="n">
         <x:f>IF('02 魂火与惩罚'!B12=0,"不扣血",ROUNDUP('02 魂火与惩罚'!B6/'02 魂火与惩罚'!B12,0))</x:f>
-        <x:v>13</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
@@ -1309,8 +1387,72 @@
         <x:v>src/runtime/director/level_boss_compiler.gd</x:v>
       </x:c>
     </x:row>
+    <x:row r="12" ht="46" customHeight="1">
+      <x:c r="A12" s="6" t="str">
+        <x:v>音符起步弹射倍率</x:v>
+      </x:c>
+      <x:c r="B12" s="21" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C12" s="20" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D12" s="6" t="str">
+        <x:v>倍</x:v>
+      </x:c>
+      <x:c r="E12" s="6" t="str">
+        <x:v>1～3</x:v>
+      </x:c>
+      <x:c r="F12" s="20" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="G12" s="8" t="str">
+        <x:v>相对巡航速度的起步速度，初段平滑回落，让音符更快离开 BOSS；不改变发射和判定时刻。</x:v>
+      </x:c>
+      <x:c r="H12" s="6" t="str">
+        <x:v>boss</x:v>
+      </x:c>
+      <x:c r="I12" s="6" t="str">
+        <x:v>launch_speed_ratio</x:v>
+      </x:c>
+      <x:c r="J12" s="6" t="str">
+        <x:v>src/runtime/director/boss_emission_path.gd</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="46" customHeight="1">
+      <x:c r="A13" s="6" t="str">
+        <x:v>BOSS 音符普通路线接入比例</x:v>
+      </x:c>
+      <x:c r="B13" s="11" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="C13" s="12" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="D13" s="6" t="str">
+        <x:v>比例</x:v>
+      </x:c>
+      <x:c r="E13" s="6" t="str">
+        <x:v>0～0.2</x:v>
+      </x:c>
+      <x:c r="F13" s="12" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="G13" s="8" t="str">
+        <x:v>0 为普通出生点，1 为判定点；默认 0.05 保留 95% 普通接近路线，长路线自动提前发射。</x:v>
+      </x:c>
+      <x:c r="H13" s="6" t="str">
+        <x:v>boss</x:v>
+      </x:c>
+      <x:c r="I13" s="6" t="str">
+        <x:v>route_join_ratio</x:v>
+      </x:c>
+      <x:c r="J13" s="6" t="str">
+        <x:v>src/runtime/director/boss_emission_path.gd</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:dataValidations count="6">
+  <x:dataValidations count="8">
     <x:dataValidation type="decimal" operator="between" sqref="B6">
       <x:formula1>0</x:formula1>
       <x:formula2>2</x:formula2>
@@ -1334,6 +1476,14 @@
     <x:dataValidation type="decimal" operator="between" sqref="B11">
       <x:formula1>0</x:formula1>
       <x:formula2>60</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="decimal" operator="between" sqref="B12">
+      <x:formula1>1</x:formula1>
+      <x:formula2>3</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="decimal" operator="between" sqref="B13">
+      <x:formula1>0</x:formula1>
+      <x:formula2>0.2</x:formula2>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1636,10 +1786,10 @@
         <x:v>女土蝠 · 下一关</x:v>
       </x:c>
       <x:c r="B6" s="50" t="str">
-        <x:v>s07</x:v>
+        <x:v>level2</x:v>
       </x:c>
       <x:c r="C6" s="47" t="str">
-        <x:v>s07</x:v>
+        <x:v>level2</x:v>
       </x:c>
       <x:c r="D6" s="6" t="str">
         <x:v>关卡 ID</x:v>
@@ -1651,7 +1801,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G6" s="8" t="str">
-        <x:v>通关后解锁并提供下一关入口。填写关卡稳定 ID；留空表示末关。仅正式关卡使用。</x:v>
+        <x:v>默认只有钟开放；钟通关解锁火，火通关解锁牲。通关不要求玄同或至臻；失败不解锁，已获解锁保留。下一关使用稳定 ID，末关留空。</x:v>
       </x:c>
       <x:c r="H6" s="6" t="str">
         <x:v>reward:tutorial2</x:v>
@@ -1732,10 +1882,10 @@
         <x:v>翼火蛇 · 下一关</x:v>
       </x:c>
       <x:c r="B9" s="50" t="str">
-        <x:v>s08</x:v>
+        <x:v>level3</x:v>
       </x:c>
       <x:c r="C9" s="47" t="str">
-        <x:v>s08</x:v>
+        <x:v>level3</x:v>
       </x:c>
       <x:c r="D9" s="6" t="str">
         <x:v>关卡 ID</x:v>
@@ -1747,16 +1897,16 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G9" s="8" t="str">
-        <x:v>通关后解锁并提供下一关入口。填写关卡稳定 ID；留空表示末关。仅正式关卡使用。</x:v>
+        <x:v>默认只有钟开放；钟通关解锁火，火通关解锁牲。通关不要求玄同或至臻；失败不解锁，已获解锁保留。下一关使用稳定 ID，末关留空。</x:v>
       </x:c>
       <x:c r="H9" s="6" t="str">
-        <x:v>reward:s07</x:v>
+        <x:v>reward:level2</x:v>
       </x:c>
       <x:c r="I9" s="6" t="str">
         <x:v>next_stage_id</x:v>
       </x:c>
       <x:c r="J9" s="6" t="str">
-        <x:v>content/stages/s07/reward_definition.tres</x:v>
+        <x:v>content/stages/level2/reward.tres</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="46" customHeight="1">
@@ -1782,13 +1932,13 @@
         <x:v>玄同授予本关对应随从的基础形态。0 关闭，1 开启；不撤回已经获得的随从。</x:v>
       </x:c>
       <x:c r="H10" s="6" t="str">
-        <x:v>reward:s07</x:v>
+        <x:v>reward:level2</x:v>
       </x:c>
       <x:c r="I10" s="6" t="str">
         <x:v>fc_grants_base_pet</x:v>
       </x:c>
       <x:c r="J10" s="6" t="str">
-        <x:v>content/stages/s07/reward_definition.tres</x:v>
+        <x:v>content/stages/level2/reward.tres</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="46" customHeight="1">
@@ -1814,13 +1964,13 @@
         <x:v>至臻授予本关对应随从的进阶形态，并保证已收服。0 关闭，1 开启。</x:v>
       </x:c>
       <x:c r="H11" s="6" t="str">
-        <x:v>reward:s07</x:v>
+        <x:v>reward:level2</x:v>
       </x:c>
       <x:c r="I11" s="6" t="str">
         <x:v>ap_grants_advanced_pet</x:v>
       </x:c>
       <x:c r="J11" s="6" t="str">
-        <x:v>content/stages/s07/reward_definition.tres</x:v>
+        <x:v>content/stages/level2/reward.tres</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="46" customHeight="1">
@@ -1839,16 +1989,16 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G12" s="8" t="str">
-        <x:v>通关后解锁并提供下一关入口。填写关卡稳定 ID；留空表示末关。仅正式关卡使用。</x:v>
+        <x:v>默认只有钟开放；钟通关解锁火，火通关解锁牲。通关不要求玄同或至臻；失败不解锁，已获解锁保留。下一关使用稳定 ID，末关留空。</x:v>
       </x:c>
       <x:c r="H12" s="6" t="str">
-        <x:v>reward:s08</x:v>
+        <x:v>reward:level3</x:v>
       </x:c>
       <x:c r="I12" s="6" t="str">
         <x:v>next_stage_id</x:v>
       </x:c>
       <x:c r="J12" s="6" t="str">
-        <x:v>content/stages/s08/reward_definition.tres</x:v>
+        <x:v>content/stages/level3/reward.tres</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="46" customHeight="1">
@@ -1874,13 +2024,13 @@
         <x:v>玄同授予本关对应随从的基础形态。0 关闭，1 开启；不撤回已经获得的随从。</x:v>
       </x:c>
       <x:c r="H13" s="6" t="str">
-        <x:v>reward:s08</x:v>
+        <x:v>reward:level3</x:v>
       </x:c>
       <x:c r="I13" s="6" t="str">
         <x:v>fc_grants_base_pet</x:v>
       </x:c>
       <x:c r="J13" s="6" t="str">
-        <x:v>content/stages/s08/reward_definition.tres</x:v>
+        <x:v>content/stages/level3/reward.tres</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="46" customHeight="1">
@@ -1906,13 +2056,13 @@
         <x:v>至臻授予本关对应随从的进阶形态，并保证已收服。0 关闭，1 开启。</x:v>
       </x:c>
       <x:c r="H14" s="6" t="str">
-        <x:v>reward:s08</x:v>
+        <x:v>reward:level3</x:v>
       </x:c>
       <x:c r="I14" s="6" t="str">
         <x:v>ap_grants_advanced_pet</x:v>
       </x:c>
       <x:c r="J14" s="6" t="str">
-        <x:v>content/stages/s08/reward_definition.tres</x:v>
+        <x:v>content/stages/level3/reward.tres</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2533,7 +2683,7 @@
       <x:c r="A14" s="6" t="str">
         <x:v>判定位置微偏移</x:v>
       </x:c>
-      <x:c r="B14" s="103" t="n">
+      <x:c r="B14" s="21" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C14" s="20" t="n">
@@ -2988,10 +3138,10 @@
         <x:v>Tap 漏击伤害</x:v>
       </x:c>
       <x:c r="B7" s="9" t="n">
-        <x:v>16</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C7" s="10" t="n">
-        <x:v>16</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D7" s="6" t="str">
         <x:v>点</x:v>
@@ -3084,10 +3234,10 @@
         <x:v>Hold 每段身体伤害</x:v>
       </x:c>
       <x:c r="B10" s="21" t="n">
-        <x:v>1.6</x:v>
+        <x:v>1.2</x:v>
       </x:c>
       <x:c r="C10" s="20" t="n">
-        <x:v>1.6</x:v>
+        <x:v>1.2</x:v>
       </x:c>
       <x:c r="D10" s="6" t="str">
         <x:v>点/段</x:v>
@@ -3148,22 +3298,22 @@
         <x:v>Ghost 漏击伤害</x:v>
       </x:c>
       <x:c r="B12" s="9" t="n">
-        <x:v>8</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C12" s="10" t="n">
-        <x:v>8</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D12" s="6" t="str">
         <x:v>点/枚</x:v>
       </x:c>
       <x:c r="E12" s="6" t="str">
-        <x:v>5～15</x:v>
+        <x:v>0～6</x:v>
       </x:c>
       <x:c r="F12" s="10" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G12" s="8" t="str">
-        <x:v>按关联调频完成情况判定；失败逐枚扣血。预测位置只作引导，不额外判相纹碰撞。</x:v>
+        <x:v>关联调频达到 Good 即可击破；失败逐枚扣血并中断 Combo、FC/AP。Ghost 独立统计并计入整关命中率，不追加基础分。预测位置只作引导。</x:v>
       </x:c>
       <x:c r="H12" s="6" t="str">
         <x:v>rules</x:v>
@@ -4866,7 +5016,7 @@
       <x:c r="A7" s="6" t="str">
         <x:v>已停用：缓流周期</x:v>
       </x:c>
-      <x:c r="B7" s="87" t="n">
+      <x:c r="B7" s="117" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="C7" s="20" t="n">
@@ -4894,7 +5044,7 @@
       <x:c r="A8" s="6" t="str">
         <x:v>已停用：水带起伏</x:v>
       </x:c>
-      <x:c r="B8" s="87" t="n">
+      <x:c r="B8" s="117" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C8" s="20" t="n">
@@ -4922,7 +5072,7 @@
       <x:c r="A9" s="6" t="str">
         <x:v>已停用：大浪回卷</x:v>
       </x:c>
-      <x:c r="B9" s="87" t="n">
+      <x:c r="B9" s="117" t="n">
         <x:v>12</x:v>
       </x:c>
       <x:c r="C9" s="20" t="n">
@@ -4950,7 +5100,7 @@
       <x:c r="A10" s="6" t="str">
         <x:v>已停用：节拍回应</x:v>
       </x:c>
-      <x:c r="B10" s="88" t="n">
+      <x:c r="B10" s="118" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C10" s="10" t="n">
@@ -4978,7 +5128,7 @@
       <x:c r="A11" s="6" t="str">
         <x:v>已停用：节拍舒张幅度</x:v>
       </x:c>
-      <x:c r="B11" s="87" t="n">
+      <x:c r="B11" s="117" t="n">
         <x:v>1.2</x:v>
       </x:c>
       <x:c r="C11" s="20" t="n">
@@ -5006,7 +5156,7 @@
       <x:c r="A12" s="6" t="str">
         <x:v>已停用：卷流接替间隔</x:v>
       </x:c>
-      <x:c r="B12" s="88" t="n">
+      <x:c r="B12" s="118" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C12" s="10" t="n">
@@ -5034,7 +5184,7 @@
       <x:c r="A13" s="6" t="str">
         <x:v>已停用：大浪高度</x:v>
       </x:c>
-      <x:c r="B13" s="87" t="n">
+      <x:c r="B13" s="117" t="n">
         <x:v>165</x:v>
       </x:c>
       <x:c r="C13" s="20" t="n">
@@ -5062,7 +5212,7 @@
       <x:c r="A14" s="6" t="str">
         <x:v>已停用：浪身推进</x:v>
       </x:c>
-      <x:c r="B14" s="87" t="n">
+      <x:c r="B14" s="117" t="n">
         <x:v>190</x:v>
       </x:c>
       <x:c r="C14" s="20" t="n">
@@ -5090,7 +5240,7 @@
       <x:c r="A15" s="6" t="str">
         <x:v>已停用：翻卷行程</x:v>
       </x:c>
-      <x:c r="B15" s="87" t="n">
+      <x:c r="B15" s="117" t="n">
         <x:v>90</x:v>
       </x:c>
       <x:c r="C15" s="20" t="n">
@@ -5118,7 +5268,7 @@
       <x:c r="A16" s="6" t="str">
         <x:v>已停用：拍落白沫强度</x:v>
       </x:c>
-      <x:c r="B16" s="89" t="n">
+      <x:c r="B16" s="119" t="n">
         <x:v>0.9</x:v>
       </x:c>
       <x:c r="C16" s="12" t="n">
@@ -5274,7 +5424,7 @@
       <x:c r="A21" s="6" t="str">
         <x:v>已停用：漩涡外半径</x:v>
       </x:c>
-      <x:c r="B21" s="87" t="n">
+      <x:c r="B21" s="117" t="n">
         <x:v>170</x:v>
       </x:c>
       <x:c r="C21" s="20" t="n">
@@ -5334,7 +5484,7 @@
       <x:c r="A23" s="6" t="str">
         <x:v>已停用：卷入角度</x:v>
       </x:c>
-      <x:c r="B23" s="87" t="n">
+      <x:c r="B23" s="117" t="n">
         <x:v>240</x:v>
       </x:c>
       <x:c r="C23" s="20" t="n">

--- a/outputs/planning/策划参数.xlsx
+++ b/outputs/planning/策划参数.xlsx
@@ -2,20 +2,21 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用与量级" sheetId="1" r:id="R59cbc99f785d411c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01 判定与容错" sheetId="2" r:id="R1a21058193124a23"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02 魂火与惩罚" sheetId="3" r:id="R7de6dbe5e6424c35"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03 调频" sheetId="4" r:id="Rcdfa93105a154074"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04 计分" sheetId="5" r:id="R0d5d2955ee204259"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05 读谱与声波" sheetId="6" r:id="R9a83d9b0b4a54f6a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06 随从" sheetId="7" r:id="R37fd2ca63ffe4ea9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07 分界线表现" sheetId="8" r:id="R5cc4e3a37fbc4452"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08 角色移动" sheetId="9" r:id="R7bfc092b2a44491f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09 BOSS 表现" sheetId="10" r:id="R1ce664e7efc44e36"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10 UI 火框" sheetId="11" r:id="R6fe492598d0349e1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11 关卡奖励" sheetId="12" r:id="Re27fa730d8504a74"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12 开屏引导" sheetId="13" r:id="R37771a89deb24655"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13 判定表现" sheetId="14" r:id="R89b01d2c5ca24186"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用与量级" sheetId="1" r:id="R50e67d05098143f3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01 判定与容错" sheetId="2" r:id="R23360d6958ef4471"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02 魂火与惩罚" sheetId="3" r:id="R27d24fb0503944f0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03 调频" sheetId="4" r:id="Ra50b44aa9d0f46e4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04 计分" sheetId="5" r:id="Rc381be0f4ce54a97"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05 读谱与声波" sheetId="6" r:id="R49a477296d7245be"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06 随从" sheetId="7" r:id="Rc1d0fcc3e07a44d2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07 分界线表现" sheetId="8" r:id="Rba68e7b4875c40a7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08 角色移动" sheetId="9" r:id="R19ad071dc2664a5a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09 BOSS 表现" sheetId="10" r:id="R83e2225aeace4520"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10 UI 火框" sheetId="11" r:id="Rab8cb75fb0264a92"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11 关卡奖励" sheetId="12" r:id="R82f2e7ec93b742be"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12 开屏引导" sheetId="13" r:id="R4741db5898bb4c96"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13 判定表现" sheetId="14" r:id="R9f1c103a41944ccd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14 计时与键位" sheetId="15" r:id="R9e01eea9c1034148"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -58,7 +59,7 @@
       <x:name val="Microsoft YaHei"/>
     </x:font>
   </x:fonts>
-  <x:fills count="43">
+  <x:fills count="56">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -270,6 +271,71 @@
         <x:fgColor rgb="FFE7E8EA"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF0C2"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE7E8EA"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF3F5967"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF0C2"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE7E8EA"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE7E8EA"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF0C2"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE7E8EA"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF0C2"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE7E8EA"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE7E8EA"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE7E8EA"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE7E8EA"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="1">
     <x:border/>
@@ -277,7 +343,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="120">
+  <x:cellXfs count="143">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -594,6 +660,71 @@
       <x:alignment vertical="center"/>
     </x:xf>
     <x:xf numFmtId="201" fontId="1" fillId="42" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="43" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="205" fontId="1" fillId="43" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="44" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="205" fontId="1" fillId="44" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="45" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="45" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="46" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="1" fillId="46" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="205" fontId="1" fillId="46" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="47" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="205" fontId="1" fillId="47" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="48" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="205" fontId="1" fillId="48" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="49" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="205" fontId="1" fillId="49" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="50" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="51" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="205" fontId="1" fillId="50" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="205" fontId="1" fillId="51" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="205" fontId="1" fillId="52" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="205" fontId="1" fillId="53" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="205" fontId="1" fillId="54" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="205" fontId="1" fillId="55" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
   </x:cellXfs>
@@ -1023,11 +1154,10 @@
     </x:row>
     <x:row r="21" ht="30" customHeight="1">
       <x:c r="A21" s="1" t="str">
-        <x:v>调频一程 1 s：满幅理想耗时（s）</x:v>
-      </x:c>
-      <x:c r="B21" s="16" t="n">
-        <x:f>MAX(1-'03 调频'!B6/1000,0.001)</x:f>
-        <x:v>0.5</x:v>
+        <x:v>调频摇杆操作</x:v>
+      </x:c>
+      <x:c r="B21" s="16" t="str">
+        <x:v>持续推住持续推进，推量控速，回中停止；帽面两端各外展15°仅供显示。</x:v>
       </x:c>
       <x:c r="C21" s="1"/>
       <x:c r="D21" s="1"/>
@@ -2738,6 +2868,173 @@
 </x:worksheet>
 </file>
 
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="13" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="13" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="15" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="30" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="72" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="32" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="40" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="58" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="2">
+      <x:c r="A2" s="2" t="str">
+        <x:v>计时与键位</x:v>
+      </x:c>
+      <x:c r="B2" s="1"/>
+      <x:c r="C2" s="1"/>
+      <x:c r="D2" s="1"/>
+      <x:c r="E2" s="1"/>
+      <x:c r="F2" s="1"/>
+      <x:c r="G2" s="1"/>
+      <x:c r="H2" s="1"/>
+      <x:c r="I2" s="1"/>
+      <x:c r="J2" s="1"/>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="1" t="str">
+        <x:v>修改黄色“当前值”，保存后重新装载关卡。比例用小数，开关用 0 / 1。</x:v>
+      </x:c>
+      <x:c r="B3" s="1"/>
+      <x:c r="C3" s="1"/>
+      <x:c r="D3" s="1"/>
+      <x:c r="E3" s="1"/>
+      <x:c r="F3" s="1"/>
+      <x:c r="G3" s="1"/>
+      <x:c r="H3" s="1"/>
+      <x:c r="I3" s="1"/>
+      <x:c r="J3" s="1"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="1"/>
+      <x:c r="B4" s="1"/>
+      <x:c r="C4" s="1"/>
+      <x:c r="D4" s="1"/>
+      <x:c r="E4" s="1"/>
+      <x:c r="F4" s="1"/>
+      <x:c r="G4" s="1"/>
+      <x:c r="H4" s="1"/>
+      <x:c r="I4" s="1"/>
+      <x:c r="J4" s="1"/>
+    </x:row>
+    <x:row r="5" ht="30" customHeight="1">
+      <x:c r="A5" s="125" t="str">
+        <x:v>参数</x:v>
+      </x:c>
+      <x:c r="B5" s="125" t="str">
+        <x:v>当前值</x:v>
+      </x:c>
+      <x:c r="C5" s="125" t="str">
+        <x:v>原型默认</x:v>
+      </x:c>
+      <x:c r="D5" s="125" t="str">
+        <x:v>单位</x:v>
+      </x:c>
+      <x:c r="E5" s="125" t="str">
+        <x:v>建议试调区间</x:v>
+      </x:c>
+      <x:c r="F5" s="125" t="str">
+        <x:v>每次建议改动</x:v>
+      </x:c>
+      <x:c r="G5" s="125" t="str">
+        <x:v>作用与注意事项</x:v>
+      </x:c>
+      <x:c r="H5" s="125" t="str">
+        <x:v>配置对象</x:v>
+      </x:c>
+      <x:c r="I5" s="125" t="str">
+        <x:v>字段名</x:v>
+      </x:c>
+      <x:c r="J5" s="125" t="str">
+        <x:v>来源（Game 内）</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="46" customHeight="1">
+      <x:c r="A6" s="6" t="str">
+        <x:v>判定圈键位不透明度</x:v>
+      </x:c>
+      <x:c r="B6" s="127" t="n">
+        <x:v>0.58</x:v>
+      </x:c>
+      <x:c r="C6" s="12" t="n">
+        <x:v>0.58</x:v>
+      </x:c>
+      <x:c r="D6" s="6" t="str">
+        <x:v>比例</x:v>
+      </x:c>
+      <x:c r="E6" s="6" t="str">
+        <x:v>45%～70%</x:v>
+      </x:c>
+      <x:c r="F6" s="12" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="G6" s="8" t="str">
+        <x:v>数值越大越实、越不透明；仅影响判定圈旁的按键提示，不改变判定圈与调频摇杆帽。</x:v>
+      </x:c>
+      <x:c r="H6" s="6" t="str">
+        <x:v>timing_cue</x:v>
+      </x:c>
+      <x:c r="I6" s="6" t="str">
+        <x:v>gate_glyph_opacity</x:v>
+      </x:c>
+      <x:c r="J6" s="6" t="str">
+        <x:v>src/content/resources/timing_cue_style.gd</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="46" customHeight="1">
+      <x:c r="A7" s="6" t="str">
+        <x:v>判定圈键位柔光强度</x:v>
+      </x:c>
+      <x:c r="B7" s="128" t="n">
+        <x:v>0.28</x:v>
+      </x:c>
+      <x:c r="C7" s="20" t="n">
+        <x:v>0.28</x:v>
+      </x:c>
+      <x:c r="D7" s="6" t="str">
+        <x:v>强度</x:v>
+      </x:c>
+      <x:c r="E7" s="6" t="str">
+        <x:v>0.15～0.4</x:v>
+      </x:c>
+      <x:c r="F7" s="20" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="G7" s="8" t="str">
+        <x:v>增强按键提示外侧柔光；光晕范围保持 6 px，色板沿用所属阵营。</x:v>
+      </x:c>
+      <x:c r="H7" s="6" t="str">
+        <x:v>timing_cue</x:v>
+      </x:c>
+      <x:c r="I7" s="6" t="str">
+        <x:v>gate_glyph_glow_strength</x:v>
+      </x:c>
+      <x:c r="J7" s="6" t="str">
+        <x:v>src/content/resources/timing_cue_style.gd</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:dataValidations count="2">
+    <x:dataValidation type="decimal" operator="between" sqref="B6">
+      <x:formula1>0</x:formula1>
+      <x:formula2>1</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="decimal" operator="between" sqref="B7">
+      <x:formula1>0</x:formula1>
+      <x:formula2>1</x:formula2>
+    </x:dataValidation>
+  </x:dataValidations>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
@@ -3313,7 +3610,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G12" s="8" t="str">
-        <x:v>关联调频达到 Good 即可击破；失败逐枚扣血并中断 Combo、FC/AP。Ghost 独立统计并计入整关命中率，不追加基础分。预测位置只作引导。</x:v>
+        <x:v>关联调频达到 Pass 即可击破且不扣血；失败逐枚扣血并中断 Combo、FC/AP。Ghost 独立统计并计入整关命中率，不追加基础分。</x:v>
       </x:c>
       <x:c r="H12" s="6" t="str">
         <x:v>rules</x:v>
@@ -3504,7 +3801,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="G6" s="8" t="str">
-        <x:v>摇杆推进速度=弧长/max(该程秒数−容错秒数,0.001)；增大更易提前完成，不延长尾点。</x:v>
+        <x:v>沿用原版速度基线：单程弧长除以（单程秒数−此余量）。它只调整推进速度，成绩仍在谱面尾点结算；短于余量的程会很快填满。</x:v>
       </x:c>
       <x:c r="H6" s="6" t="str">
         <x:v>rules</x:v>
@@ -3536,7 +3833,7 @@
         <x:v>0.01</x:v>
       </x:c>
       <x:c r="G7" s="8" t="str">
-        <x:v>死区外按 (幅度−死区)/(1−死区) 线性映射速度；越大越抗漂移。</x:v>
+        <x:v>死区内停止累积；死区外推量线性控速，沿原版游标切线投影，持续推住持续推进。引导帽面两端各外展15°仅供显示，不参与输入。</x:v>
       </x:c>
       <x:c r="H7" s="6" t="str">
         <x:v>rules</x:v>
@@ -3568,7 +3865,7 @@
         <x:v>0.005</x:v>
       </x:c>
       <x:c r="G8" s="8" t="str">
-        <x:v>端点吸附与视觉捕获区，另用于 Ghost 区间内引导进度的容差；Tuning 终点评分读取完成度阈值。</x:v>
+        <x:v>端点视觉吸附与观察区，不参与 Ghost Pass 容错；Tuning 终点评分读取完成度阈值。</x:v>
       </x:c>
       <x:c r="H8" s="6" t="str">
         <x:v>rules</x:v>
@@ -3824,7 +4121,7 @@
         <x:v>0.01</x:v>
       </x:c>
       <x:c r="G16" s="8" t="str">
-        <x:v>不足 Perfect 时达到此比例记 Good；不增加晚到窗口。</x:v>
+        <x:v>尾点 Good 最低完成比例；不足 Perfect 时达到此值记 Good，不增加晚到窗口。Ghost 击碎底线使用 Pass 完成度。</x:v>
       </x:c>
       <x:c r="H16" s="6" t="str">
         <x:v>rules</x:v>
@@ -3856,7 +4153,7 @@
         <x:v>0.01</x:v>
       </x:c>
       <x:c r="G17" s="8" t="str">
-        <x:v>最低成功比例；低于此值或松开记 Miss。关联 Hold 失败后滑条淡出，仍按原时刻结算；仅 Ghost 扣血。</x:v>
+        <x:v>尾点 Pass 与 Ghost 击碎底线；中途允许落后整程的1−此值，提前有效。仍须持有；仅 Ghost 漏击扣血，关联 Hold 失败后滑条淡出。</x:v>
       </x:c>
       <x:c r="H17" s="6" t="str">
         <x:v>rules</x:v>
@@ -3868,8 +4165,68 @@
         <x:v>src/content/resources/gameplay_rule_set.gd</x:v>
       </x:c>
     </x:row>
+    <x:row r="18" ht="46" customHeight="1">
+      <x:c r="A18" s="6" t="str">
+        <x:v>摇杆推进倍率</x:v>
+      </x:c>
+      <x:c r="B18" s="21" t="n">
+        <x:v>1.02</x:v>
+      </x:c>
+      <x:c r="C18" s="20" t="n">
+        <x:v>1.02</x:v>
+      </x:c>
+      <x:c r="D18" s="6" t="str">
+        <x:v>倍</x:v>
+      </x:c>
+      <x:c r="E18" s="6" t="str">
+        <x:v>1.00～1.05</x:v>
+      </x:c>
+      <x:c r="F18" s="20" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="G18" s="8" t="str">
+        <x:v>在原版速度公式上乘此倍率；1.02仅快2%。持续推住随时间累积，推量控制速度，回中停止。与角度对应位置无关。</x:v>
+      </x:c>
+      <x:c r="H18" s="6" t="str">
+        <x:v>rules</x:v>
+      </x:c>
+      <x:c r="I18" s="6" t="str">
+        <x:v>tuning_progress_speed_multiplier</x:v>
+      </x:c>
+      <x:c r="J18" s="6" t="str">
+        <x:v>src/content/resources/gameplay_rule_set.gd</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="46" customHeight="1">
+      <x:c r="A19" s="6" t="str">
+        <x:v>已停用：摇杆角度助推</x:v>
+      </x:c>
+      <x:c r="B19" s="142" t="n">
+        <x:v>1.03</x:v>
+      </x:c>
+      <x:c r="C19" s="20" t="n">
+        <x:v>1.03</x:v>
+      </x:c>
+      <x:c r="D19" s="6" t="str">
+        <x:v>倍</x:v>
+      </x:c>
+      <x:c r="E19" s="6" t="str">
+        <x:v>1.00～1.05</x:v>
+      </x:c>
+      <x:c r="F19" s="20" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="G19" s="8" t="str">
+        <x:v>已恢复速度累积。旧角度助推不再生效，使用摇杆推进倍率。</x:v>
+      </x:c>
+      <x:c r="H19" s="6" t="str"/>
+      <x:c r="I19" s="6" t="str"/>
+      <x:c r="J19" s="6" t="str">
+        <x:v>src/content/resources/gameplay_rule_set.gd</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:dataValidations count="12">
+  <x:dataValidations count="14">
     <x:dataValidation type="whole" operator="between" sqref="B6">
       <x:formula1>0</x:formula1>
       <x:formula2>2000</x:formula2>
@@ -3917,6 +4274,14 @@
     <x:dataValidation type="decimal" operator="between" sqref="B17">
       <x:formula1>0</x:formula1>
       <x:formula2>1</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="decimal" operator="between" sqref="B18">
+      <x:formula1>1</x:formula1>
+      <x:formula2>1.1</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="decimal" operator="between" sqref="B19">
+      <x:formula1>1</x:formula1>
+      <x:formula2>1.1</x:formula2>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4342,7 +4707,7 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="G6" s="8" t="str">
-        <x:v>生成至判定点的时间；增大能更早看见音符，且改变速度与接触几何。</x:v>
+        <x:v>普通音符从生成到判定点的时间；调频整组预告取其64%（默认1.44秒），大圈与滑条同步出现。</x:v>
       </x:c>
       <x:c r="H6" s="6" t="str">
         <x:v>rules</x:v>

--- a/outputs/planning/策划参数.xlsx
+++ b/outputs/planning/策划参数.xlsx
@@ -2,21 +2,21 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用与量级" sheetId="1" r:id="R50e67d05098143f3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01 判定与容错" sheetId="2" r:id="R23360d6958ef4471"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02 魂火与惩罚" sheetId="3" r:id="R27d24fb0503944f0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03 调频" sheetId="4" r:id="Ra50b44aa9d0f46e4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04 计分" sheetId="5" r:id="Rc381be0f4ce54a97"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05 读谱与声波" sheetId="6" r:id="R49a477296d7245be"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06 随从" sheetId="7" r:id="Rc1d0fcc3e07a44d2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07 分界线表现" sheetId="8" r:id="Rba68e7b4875c40a7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08 角色移动" sheetId="9" r:id="R19ad071dc2664a5a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09 BOSS 表现" sheetId="10" r:id="R83e2225aeace4520"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10 UI 火框" sheetId="11" r:id="Rab8cb75fb0264a92"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11 关卡奖励" sheetId="12" r:id="R82f2e7ec93b742be"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12 开屏引导" sheetId="13" r:id="R4741db5898bb4c96"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13 判定表现" sheetId="14" r:id="R9f1c103a41944ccd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14 计时与键位" sheetId="15" r:id="R9e01eea9c1034148"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用与量级" sheetId="1" r:id="Rc7bfa8b042fc48dd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01 判定与容错" sheetId="2" r:id="Re54d5714d5024069"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02 魂火与惩罚" sheetId="3" r:id="Rd93ec8e806f5490a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03 调频" sheetId="4" r:id="R42b74a2c8ba340e6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04 计分" sheetId="5" r:id="Ra33cacacb4974398"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05 读谱与声波" sheetId="6" r:id="R59b3395d846347d2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06 随从" sheetId="7" r:id="Rf2db37a95d564cfe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07 分界线表现" sheetId="8" r:id="R5cdf56a7123e4890"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08 角色移动" sheetId="9" r:id="Rd8084f82a53a448f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09 BOSS 表现" sheetId="10" r:id="R0f14f925f5d24a84"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10 UI 火框" sheetId="11" r:id="R2b33eb7b1d9f4db6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11 关卡奖励" sheetId="12" r:id="Reb0b1bb6a39d4a3a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12 开屏引导" sheetId="13" r:id="Rf2e6192856d84268"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13 判定表现" sheetId="14" r:id="Rc33047e39bcc4f98"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14 计时与键位" sheetId="15" r:id="R2e8a6578d5e84806"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1345,7 +1345,7 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="G6" s="8" t="str">
-        <x:v>调整光波、火焰、眼光及羊头裂光和白场。攻击不提亮手部，默认白场保持0.5秒。</x:v>
+        <x:v>调整光波、火焰、眼光、羊头裂光及素材白场。第三关结算白场固定全白停留0.5秒，不受此倍率影响。</x:v>
       </x:c>
       <x:c r="H6" s="6" t="str">
         <x:v>boss</x:v>
